--- a/tracker/Job_Leads_Tracker.xlsx
+++ b/tracker/Job_Leads_Tracker.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1662" uniqueCount="1056">
   <si>
     <t>Lead ID</t>
   </si>
@@ -709,241 +709,2392 @@
     <t>L021</t>
   </si>
   <si>
+    <t>Supabase</t>
+  </si>
+  <si>
+    <t>https://supabase.com</t>
+  </si>
+  <si>
+    <t>Open-source Firebase alternative providing Postgres, Auth, Realtime, and Edge Functions.</t>
+  </si>
+  <si>
+    <t>Actively hiring remote Product Engineers; series B high-growth developer platform.</t>
+  </si>
+  <si>
+    <t>Paul Copplestone</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/paulcopplestone</t>
+  </si>
+  <si>
+    <t>https://supabase.com/careers</t>
+  </si>
+  <si>
+    <t>Review Supabase Studio UI codebase on GitHub and draft tailored pitch to Paul Copplestone</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide company. Heavy use of TypeScript, Next.js, and Postgres. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L022</t>
   </si>
   <si>
+    <t>Vercel</t>
+  </si>
+  <si>
+    <t>https://vercel.com</t>
+  </si>
+  <si>
+    <t>Cloud platform for frontend developers and creators of Next.js.</t>
+  </si>
+  <si>
+    <t>Continuous hiring for Design Engineers and Product Engineers on v0 and core dashboard.</t>
+  </si>
+  <si>
+    <t>Guillermo Rauch</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rauchg</t>
+  </si>
+  <si>
+    <t>https://vercel.com/careers</t>
+  </si>
+  <si>
+    <t>Prepare interactive micro-demo showcasing Next.js App Router performance and message Guillermo Rauch</t>
+  </si>
+  <si>
+    <t>Global remote team with strong emphasis on UI craftsmanship, micro-interactions, and design systems. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L023</t>
   </si>
   <si>
+    <t>Resend</t>
+  </si>
+  <si>
+    <t>https://resend.com</t>
+  </si>
+  <si>
+    <t>Modern developer-first email delivery and notification API.</t>
+  </si>
+  <si>
+    <t>Expanding product engineering and React Email ecosystem; Y Combinator company.</t>
+  </si>
+  <si>
+    <t>Zeno Rocha</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/zenorocha</t>
+  </si>
+  <si>
+    <t>https://resend.com/careers</t>
+  </si>
+  <si>
+    <t>Check open product engineering roles and write personalized note to Zeno Rocha referencing React Email</t>
+  </si>
+  <si>
+    <t>Remote-first global company. Focuses on developer experience and high aesthetics. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L024</t>
   </si>
   <si>
+    <t>Raycast</t>
+  </si>
+  <si>
+    <t>https://raycast.com</t>
+  </si>
+  <si>
+    <t>Blazingly fast, extendable launcher and desktop productivity platform.</t>
+  </si>
+  <si>
+    <t>Regularly recruits Product Engineers and Design Engineers for web, mobile, and API extensions.</t>
+  </si>
+  <si>
+    <t>Thomas Paul Mann</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/thomaspaulmann</t>
+  </si>
+  <si>
+    <t>https://raycast.com/careers</t>
+  </si>
+  <si>
+    <t>Build and publish a sample Raycast extension and share demo with Thomas Mann</t>
+  </si>
+  <si>
+    <t>Distributed team across Europe and worldwide. Extremely high standard for client-side speed. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L025</t>
   </si>
   <si>
+    <t>PostHog</t>
+  </si>
+  <si>
+    <t>https://posthog.com</t>
+  </si>
+  <si>
+    <t>All-in-one open-source product analytics, session replay, and feature flagging platform.</t>
+  </si>
+  <si>
+    <t>Transparent remote hiring handbook; actively posts Full-stack Product Engineer roles on posthog.com/careers.</t>
+  </si>
+  <si>
+    <t>James Hawkins</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/james-hawkins-9941a541</t>
+  </si>
+  <si>
+    <t>https://posthog.com/careers</t>
+  </si>
+  <si>
+    <t>Complete small open-source issue on PostHog GitHub repo before submitting application</t>
+  </si>
+  <si>
+    <t>100% transparent compensation and remote-first worldwide hiring model. Uses React, TypeScript, Python/Django, ClickHouse. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L026</t>
   </si>
   <si>
+    <t>Cal.com</t>
+  </si>
+  <si>
+    <t>https://cal.com</t>
+  </si>
+  <si>
+    <t>Open-source scheduling infrastructure and customizable calendar platform.</t>
+  </si>
+  <si>
+    <t>Growing open-source team; recruits Product Engineers across GitHub and Ashby.</t>
+  </si>
+  <si>
+    <t>Peer Richelsen</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/peer-richelsen</t>
+  </si>
+  <si>
+    <t>https://cal.com/careers</t>
+  </si>
+  <si>
+    <t>Review Cal.com mobile integration and draft outreach to Peer Richelsen</t>
+  </si>
+  <si>
+    <t>Fully remote, open-source commercial software. TypeScript, Next.js, Prisma, Tailwind stack. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L027</t>
   </si>
   <si>
+    <t>Dub.co</t>
+  </si>
+  <si>
+    <t>https://dub.co</t>
+  </si>
+  <si>
+    <t>Open-source link management and conversion attribution platform for modern marketing teams.</t>
+  </si>
+  <si>
+    <t>High-velocity shipping; hiring Product Engineers and Design Engineers.</t>
+  </si>
+  <si>
+    <t>Steven Tey</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/steventey</t>
+  </si>
+  <si>
+    <t>https://dub.co/careers</t>
+  </si>
+  <si>
+    <t>Inspect Dub link-preview component architecture and send feedback to Steven Tey</t>
+  </si>
+  <si>
+    <t>Built in public by Steven Tey. Exceptional UI aesthetics, micro-interactions, Next.js, Tailwind. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L028</t>
   </si>
   <si>
+    <t>Railway</t>
+  </si>
+  <si>
+    <t>https://railway.app</t>
+  </si>
+  <si>
+    <t>Instant infrastructure platform that deploys code, databases, and microservices.</t>
+  </si>
+  <si>
+    <t>Regularly recruits Product Engineers who love developer infrastructure and web apps.</t>
+  </si>
+  <si>
+    <t>Jake Cooper</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jake-cooper-73b32439</t>
+  </si>
+  <si>
+    <t>https://railway.app/careers</t>
+  </si>
+  <si>
+    <t>Deploy a live project on Railway and reach out to engineering lead with feedback</t>
+  </si>
+  <si>
+    <t>Remote-first team with worldwide contractor support. Focuses on DX and infrastructure automation. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L029</t>
   </si>
   <si>
+    <t>Convex</t>
+  </si>
+  <si>
+    <t>https://convex.dev</t>
+  </si>
+  <si>
+    <t>The reactive backend-as-a-service platform with automatic caching and real-time sync.</t>
+  </si>
+  <si>
+    <t>Actively hiring Product Engineers to build developer onboarding, dashboards, and templates.</t>
+  </si>
+  <si>
+    <t>Sujay Jayakar</t>
+  </si>
+  <si>
+    <t>CTO</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sujayjayakar</t>
+  </si>
+  <si>
+    <t>https://convex.dev/careers</t>
+  </si>
+  <si>
+    <t>Build a small real-time React Native demo on Convex and contact Sujay Jayakar</t>
+  </si>
+  <si>
+    <t>Backed by a16z. Values deep technical fundamentals and clean developer interfaces. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L030</t>
   </si>
   <si>
+    <t>Attio</t>
+  </si>
+  <si>
+    <t>https://attio.com</t>
+  </si>
+  <si>
+    <t>Powerful, real-time CRM platform built specifically for modern technology companies.</t>
+  </si>
+  <si>
+    <t>Rapidly scaling engineering team across web application, mobile, and sync architecture.</t>
+  </si>
+  <si>
+    <t>Nicolas Sharp</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/nicolas-sharp</t>
+  </si>
+  <si>
+    <t>https://attio.com/careers</t>
+  </si>
+  <si>
+    <t>Study Attio data-table interactions and send feedback to design/product leads</t>
+  </si>
+  <si>
+    <t>London HQ with remote EMEA hiring. Known for world-class web UX and spreadsheet-like reactivity. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L031</t>
   </si>
   <si>
+    <t>Clerk</t>
+  </si>
+  <si>
+    <t>https://clerk.com</t>
+  </si>
+  <si>
+    <t>Complete user authentication, session management, and user profile management platform.</t>
+  </si>
+  <si>
+    <t>Aggressive engineering expansion for frontend and React Native/Expo SDKs.</t>
+  </si>
+  <si>
+    <t>Colin Sidoti</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/colin-sidoti</t>
+  </si>
+  <si>
+    <t>https://clerk.com/careers</t>
+  </si>
+  <si>
+    <t>Review Clerk Expo SDK documentation and reach out regarding mobile auth improvements</t>
+  </si>
+  <si>
+    <t>Remote-first global company. High overlap with React Native and modern frontend tooling. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L032</t>
   </si>
   <si>
+    <t>Neon</t>
+  </si>
+  <si>
+    <t>https://neon.tech</t>
+  </si>
+  <si>
+    <t>Serverless, autoscaling Postgres database with instant branching and bottomless storage.</t>
+  </si>
+  <si>
+    <t>Hiring Product Engineers for Cloud Console, developer APIs, and integrations.</t>
+  </si>
+  <si>
+    <t>Nikita Shamgunov</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/nikita-shamgunov-2b36b0</t>
+  </si>
+  <si>
+    <t>https://neon.tech/careers</t>
+  </si>
+  <si>
+    <t>Draft message to Neon product team showing automated database branching integration</t>
+  </si>
+  <si>
+    <t>Global remote-first team. Massive adoption among Next.js and serverless developers. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L033</t>
   </si>
   <si>
+    <t>PlanetScale</t>
+  </si>
+  <si>
+    <t>https://planetscale.com</t>
+  </si>
+  <si>
+    <t>High-concurrency serverless database platform built on Vitess.</t>
+  </si>
+  <si>
+    <t>Recruits engineers who appreciate developer ergonomics and rock-solid reliability.</t>
+  </si>
+  <si>
+    <t>Sam Lambert</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/samlambert</t>
+  </si>
+  <si>
+    <t>https://planetscale.com/careers</t>
+  </si>
+  <si>
+    <t>Review PlanetScale CLI and dashboard DX and prepare message to Sam Lambert</t>
+  </si>
+  <si>
+    <t>Global remote culture. Focuses on horizontal database scaling and clean UI. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L034</t>
   </si>
   <si>
+    <t>Fly.io</t>
+  </si>
+  <si>
+    <t>https://fly.io</t>
+  </si>
+  <si>
+    <t>Public cloud platform that transforms Docker containers into microVMs close to users.</t>
+  </si>
+  <si>
+    <t>Regular hiring posts on Hacker News for product and infrastructure engineers.</t>
+  </si>
+  <si>
+    <t>Kurt Mackey</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kurt-mackey-68b0871</t>
+  </si>
+  <si>
+    <t>https://fly.io/jobs</t>
+  </si>
+  <si>
+    <t>Engage with Fly.io team on public community forum before pitching</t>
+  </si>
+  <si>
+    <t>100% remote-first worldwide hiring with deep engineering blogging culture. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L035</t>
   </si>
   <si>
+    <t>Incident.io</t>
+  </si>
+  <si>
+    <t>https://incident.io</t>
+  </si>
+  <si>
+    <t>Modern incident management and response platform directly integrated with Slack and Teams.</t>
+  </si>
+  <si>
+    <t>Series B funding; expanding product engineering and mobile incident management tools.</t>
+  </si>
+  <si>
+    <t>Stephen Whitworth</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/swhitworth</t>
+  </si>
+  <si>
+    <t>https://incident.io/careers</t>
+  </si>
+  <si>
+    <t>Review Incident.io mobile app features and prepare outreach to Stephen Whitworth</t>
+  </si>
+  <si>
+    <t>HQ in London with remote EMEA team. Values high product velocity and clear communication. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L036</t>
   </si>
   <si>
+    <t>Trigger.dev</t>
+  </si>
+  <si>
+    <t>https://trigger.dev</t>
+  </si>
+  <si>
+    <t>Open-source background jobs framework for Next.js, Node.js, and TypeScript.</t>
+  </si>
+  <si>
+    <t>Hiring Product Engineers to build workflow monitoring and visual execution logs.</t>
+  </si>
+  <si>
+    <t>Matt Aitken</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mattaitken</t>
+  </si>
+  <si>
+    <t>https://trigger.dev/careers</t>
+  </si>
+  <si>
+    <t>Build a real background job workflow using Trigger.dev and reach out to Matt Aitken</t>
+  </si>
+  <si>
+    <t>Open-source developer platform. Heavy alignment with background queues and distributed tasks. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L037</t>
   </si>
   <si>
+    <t>Inngest</t>
+  </si>
+  <si>
+    <t>https://inngest.com</t>
+  </si>
+  <si>
+    <t>Event-driven durable execution engine and serverless workflow orchestrator.</t>
+  </si>
+  <si>
+    <t>Actively recruiting Product Engineers to build developer tooling and execution UI.</t>
+  </si>
+  <si>
+    <t>Tony Holdstock-Brown</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tonyhb</t>
+  </si>
+  <si>
+    <t>https://inngest.com/careers</t>
+  </si>
+  <si>
+    <t>Review Inngest step-function SDK and draft technical message to Tony Holdstock-Brown</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide. Direct domain relevance to background jobs and async state. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L038</t>
   </si>
   <si>
+    <t>Liveblocks</t>
+  </si>
+  <si>
+    <t>https://liveblocks.io</t>
+  </si>
+  <si>
+    <t>Real-time collaborative infrastructure (presence, comments, storage) for web applications.</t>
+  </si>
+  <si>
+    <t>Actively seeking Design Engineers to build collaborative UI components and documentation.</t>
+  </si>
+  <si>
+    <t>Steven Fabre</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/stevenfabre</t>
+  </si>
+  <si>
+    <t>https://liveblocks.io/careers</t>
+  </si>
+  <si>
+    <t>Prepare a demo showing Liveblocks multi-user cursor sync and reach out to Steven Fabre</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide team. Exceptional standard for web animation, design tokens, and components. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L039</t>
   </si>
   <si>
+    <t>Loops</t>
+  </si>
+  <si>
+    <t>https://loops.so</t>
+  </si>
+  <si>
+    <t>Email marketing and transactional messaging platform tailored for modern SaaS companies.</t>
+  </si>
+  <si>
+    <t>Growing product engineering team; hires remotely through Twitter/LinkedIn announcements.</t>
+  </si>
+  <si>
+    <t>Chris Frantz</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/chrisfrantz</t>
+  </si>
+  <si>
+    <t>https://loops.so/careers</t>
+  </si>
+  <si>
+    <t>Draft personalized note to Chris Frantz highlighting fullstack product delivery skills</t>
+  </si>
+  <si>
+    <t>Fast-moving YC startup. High aesthetic quality and focus on simple, reliable developer software. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L040</t>
   </si>
   <si>
+    <t>Campsite</t>
+  </si>
+  <si>
+    <t>https://campsite.com</t>
+  </si>
+  <si>
+    <t>Async communication and project feed platform for high-performance product teams.</t>
+  </si>
+  <si>
+    <t>Founded by former GitHub/Coinbase design engineers; regularly hires design-minded engineers.</t>
+  </si>
+  <si>
+    <t>Brian Lovin</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/brianlovin</t>
+  </si>
+  <si>
+    <t>https://campsite.com/careers</t>
+  </si>
+  <si>
+    <t>Study Campsite desktop and web interface flows and share feedback with Brian Lovin</t>
+  </si>
+  <si>
+    <t>World-class design engineering standards. Uses React Native Web and TypeScript. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L041</t>
   </si>
   <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>https://height.app</t>
+  </si>
+  <si>
+    <t>Autonomous project management tool leveraging AI for automatic task triaging and updates.</t>
+  </si>
+  <si>
+    <t>Actively hires Product Engineers and Design Engineers to work on reactive canvas and tables.</t>
+  </si>
+  <si>
+    <t>Michael Villar</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/michaelvillar</t>
+  </si>
+  <si>
+    <t>https://height.app/careers</t>
+  </si>
+  <si>
+    <t>Review Height spreadsheet-like interactions and send pitch to Michael Villar</t>
+  </si>
+  <si>
+    <t>Founded by former Stripe designer Michael Villar. Incredible animations and frontend performance. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L042</t>
   </si>
   <si>
+    <t>June.so</t>
+  </si>
+  <si>
+    <t>https://june.so</t>
+  </si>
+  <si>
+    <t>Automated product analytics platform built on top of Segment and PostHog for B2B SaaS.</t>
+  </si>
+  <si>
+    <t>Y Combinator company; hiring remote Product Engineers to build customer insights and feeds.</t>
+  </si>
+  <si>
+    <t>Enzo Avigo</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/enzo-avigo</t>
+  </si>
+  <si>
+    <t>https://june.so/careers</t>
+  </si>
+  <si>
+    <t>Draft message to Enzo Avigo explaining how June product metrics could integrate with mobile apps</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide culture. Focuses on actionable product analytics over raw vanity charts. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L043</t>
   </si>
   <si>
+    <t>Granola</t>
+  </si>
+  <si>
+    <t>https://granola.ai</t>
+  </si>
+  <si>
+    <t>AI-assisted meeting notepad that combines human notes with audio transcription.</t>
+  </si>
+  <si>
+    <t>Viral growth; actively recruiting Product Engineers with desktop and frontend experience.</t>
+  </si>
+  <si>
+    <t>Chris Pedregal</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/cpedregal</t>
+  </si>
+  <si>
+    <t>https://granola.ai/careers</t>
+  </si>
+  <si>
+    <t>Test Granola app flow and draft feedback message to Chris Pedregal</t>
+  </si>
+  <si>
+    <t>London HQ with remote EMEA support. Fast-growing AI productivity product. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L044</t>
   </si>
   <si>
+    <t>Warp</t>
+  </si>
+  <si>
+    <t>https://warp.dev</t>
+  </si>
+  <si>
+    <t>Modern, AI-integrated terminal built in Rust with IDE-style text editing and workflows.</t>
+  </si>
+  <si>
+    <t>Expanding web application, cloud sharing, and cross-platform clients.</t>
+  </si>
+  <si>
+    <t>Zach Lloyd</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/zachlloyd</t>
+  </si>
+  <si>
+    <t>https://warp.dev/careers</t>
+  </si>
+  <si>
+    <t>Prepare outreach to Zach Lloyd highlighting developer tooling fluency</t>
+  </si>
+  <si>
+    <t>Backed by GV and Coatue. High engineering craftsmanship bar. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L045</t>
   </si>
   <si>
+    <t>Mintlify</t>
+  </si>
+  <si>
+    <t>https://mintlify.com</t>
+  </si>
+  <si>
+    <t>Modern, automated documentation platform for developer products and open-source projects.</t>
+  </si>
+  <si>
+    <t>Fast-scaling YC startup; hiring Product Engineers to build doc engines and AI search.</t>
+  </si>
+  <si>
+    <t>Han Wang</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/han-wang-dev</t>
+  </si>
+  <si>
+    <t>https://mintlify.com/careers</t>
+  </si>
+  <si>
+    <t>Review Mintlify documentation UI components and message Han Wang with ideas</t>
+  </si>
+  <si>
+    <t>Fully remote-first worldwide hiring. Uses Next.js, MDX, Tailwind, TypeScript. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L046</t>
   </si>
   <si>
+    <t>Inkeep</t>
+  </si>
+  <si>
+    <t>https://inkeep.com</t>
+  </si>
+  <si>
+    <t>AI search, chat, and support agents for technical developer products.</t>
+  </si>
+  <si>
+    <t>Rapid adoption across major developer platforms; hiring remote full-stack product engineers.</t>
+  </si>
+  <si>
+    <t>Robert Balicki</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/robertbalicki</t>
+  </si>
+  <si>
+    <t>https://inkeep.com/careers</t>
+  </si>
+  <si>
+    <t>Test Inkeep widget integration and draft pitch to Robert Balicki</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide. High focus on LLM agent reliability and frontend widgets. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L047</t>
   </si>
   <si>
+    <t>OpenPhone</t>
+  </si>
+  <si>
+    <t>https://openphone.com</t>
+  </si>
+  <si>
+    <t>Collaborative business phone system and customer messaging app for startups.</t>
+  </si>
+  <si>
+    <t>Hiring Product Engineers and Mobile Engineers (React Native / iOS / Android).</t>
+  </si>
+  <si>
+    <t>Mahyar Raissi</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mahyarraissi</t>
+  </si>
+  <si>
+    <t>https://openphone.com/careers</t>
+  </si>
+  <si>
+    <t>Prepare outreach highlighting React Native mobile architecture from Rota project</t>
+  </si>
+  <si>
+    <t>100% remote-first company across Americas and Europe. Strong mobile product focus. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L048</t>
   </si>
   <si>
+    <t>Reflect</t>
+  </si>
+  <si>
+    <t>https://reflect.app</t>
+  </si>
+  <si>
+    <t>Fast, end-to-end encrypted networked note-taking application.</t>
+  </si>
+  <si>
+    <t>Lean, profitable product-led business by Alex MacCaw; hires skilled product generalists.</t>
+  </si>
+  <si>
+    <t>Alex MacCaw</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/alex-maccaw-83818b8</t>
+  </si>
+  <si>
+    <t>https://reflect.app/careers</t>
+  </si>
+  <si>
+    <t>Send a note to Alex MacCaw highlighting offline-first mobile sync experience</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide. Founder wrote JavaScript Web Applications and co-founded Clearbit. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L049</t>
   </si>
   <si>
+    <t>Rows</t>
+  </si>
+  <si>
+    <t>https://rows.com</t>
+  </si>
+  <si>
+    <t>Next-generation collaborative spreadsheet with built-in data integrations and AI.</t>
+  </si>
+  <si>
+    <t>Actively recruiting Product Engineers and Design Engineers for web and mobile.</t>
+  </si>
+  <si>
+    <t>Humberto Ayres Pereira</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/humberto-ayres-pereira</t>
+  </si>
+  <si>
+    <t>https://rows.com/careers</t>
+  </si>
+  <si>
+    <t>Review Rows spreadsheet computation grid and draft pitch to Humberto Pereira</t>
+  </si>
+  <si>
+    <t>Remote-first across Europe and global contractor locations. Heavy spreadsheet grid engineering. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L050</t>
   </si>
   <si>
+    <t>Daily.co</t>
+  </si>
+  <si>
+    <t>https://daily.co</t>
+  </si>
+  <si>
+    <t>Developer platform and WebRTC APIs for real-time video, audio, and AI conversation.</t>
+  </si>
+  <si>
+    <t>Recruiting Product Engineers to build customer dashboards and video SDK wrappers.</t>
+  </si>
+  <si>
+    <t>Kwin Kramer</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kwin</t>
+  </si>
+  <si>
+    <t>https://daily.co/jobs</t>
+  </si>
+  <si>
+    <t>Build a small real-time video room demo and message Kwin Kramer</t>
+  </si>
+  <si>
+    <t>100% remote-first worldwide hiring with competitive global compensation. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L051</t>
   </si>
   <si>
+    <t>Stream</t>
+  </si>
+  <si>
+    <t>https://getstream.io</t>
+  </si>
+  <si>
+    <t>Enterprise chat, activity feed, and video APIs powering over a billion end users.</t>
+  </si>
+  <si>
+    <t>Actively recruiting React Native and mobile Product Engineers for SDK maintenance.</t>
+  </si>
+  <si>
+    <t>Thierry Schellenbach</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/thierryschellenbach</t>
+  </si>
+  <si>
+    <t>https://getstream.io/team/#jobs</t>
+  </si>
+  <si>
+    <t>Highlight Rota activity feed cursor pagination benchmarks in message to Stream team</t>
+  </si>
+  <si>
+    <t>Worldwide remote hiring with presence in Amsterdam and US. Deep relevance to activity feeds. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L052</t>
   </si>
   <si>
+    <t>Knock</t>
+  </si>
+  <si>
+    <t>https://knock.app</t>
+  </si>
+  <si>
+    <t>Flexible notification infrastructure and multi-channel delivery engine for developers.</t>
+  </si>
+  <si>
+    <t>Series A startup; regularly recruiting remote Product Engineers across Ashby.</t>
+  </si>
+  <si>
+    <t>Sam Seely</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sam-seely</t>
+  </si>
+  <si>
+    <t>https://knock.app/careers</t>
+  </si>
+  <si>
+    <t>Review Knock notification feed component and message Sam Seely</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide. Built by former Segment/Frame engineering leaders. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L053</t>
   </si>
   <si>
+    <t>Novu</t>
+  </si>
+  <si>
+    <t>https://novu.co</t>
+  </si>
+  <si>
+    <t>Open-source notification center and multi-channel workflow builder.</t>
+  </si>
+  <si>
+    <t>High GitHub star velocity; actively recruits open-source contributors and product engineers.</t>
+  </si>
+  <si>
+    <t>Tomer Barnea</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tomerbarnea</t>
+  </si>
+  <si>
+    <t>https://novu.co/careers</t>
+  </si>
+  <si>
+    <t>Contribute a small documentation or UI fix on Novu repo before contacting Tomer Barnea</t>
+  </si>
+  <si>
+    <t>100% remote-first, open-source company. Strong community on Discord and GitHub. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L054</t>
   </si>
   <si>
+    <t>Medusa</t>
+  </si>
+  <si>
+    <t>https://medusajs.com</t>
+  </si>
+  <si>
+    <t>Open-source modular commerce framework built on Node.js and TypeScript.</t>
+  </si>
+  <si>
+    <t>Series A open-source company expanding core framework and Next.js storefront tooling.</t>
+  </si>
+  <si>
+    <t>Sebastian Rindom</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/sebastian-rindom</t>
+  </si>
+  <si>
+    <t>https://medusajs.com/careers</t>
+  </si>
+  <si>
+    <t>Explore Medusa 2.0 architecture and draft pitch to Sebastian Rindom</t>
+  </si>
+  <si>
+    <t>Remote-friendly across Europe and global contributors. Node.js, TypeScript, PostgreSQL. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L055</t>
   </si>
   <si>
+    <t>Payload CMS</t>
+  </si>
+  <si>
+    <t>https://payloadcms.com</t>
+  </si>
+  <si>
+    <t>TypeScript-native headless CMS and application framework integrated directly into Next.js.</t>
+  </si>
+  <si>
+    <t>Rapid adoption following Payload 3.0 launch; hiring remote full-stack engineers.</t>
+  </si>
+  <si>
+    <t>James Mikrut</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/james-mikrut</t>
+  </si>
+  <si>
+    <t>https://payloadcms.com/careers</t>
+  </si>
+  <si>
+    <t>Build a small Payload CMS collection and reach out to James Mikrut</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide. High overlap with Next.js, React, TypeScript, and MongoDB/Postgres. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L056</t>
   </si>
   <si>
+    <t>Directus</t>
+  </si>
+  <si>
+    <t>https://directus.io</t>
+  </si>
+  <si>
+    <t>Open-source backend-as-a-service providing instant REST and GraphQL APIs over SQL databases.</t>
+  </si>
+  <si>
+    <t>Global remote team hiring Product Engineers and UI/UX designers.</t>
+  </si>
+  <si>
+    <t>Ben Haynes</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/benhaynes</t>
+  </si>
+  <si>
+    <t>https://directus.io/careers</t>
+  </si>
+  <si>
+    <t>Review Directus Vue/TypeScript app modules and connect with Ben Haynes</t>
+  </si>
+  <si>
+    <t>Remote-first global hiring model with transparent pay. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L057</t>
   </si>
   <si>
+    <t>Turso</t>
+  </si>
+  <si>
+    <t>https://turso.tech</t>
+  </si>
+  <si>
+    <t>Edge database platform built on libSQL (open-source fork of SQLite).</t>
+  </si>
+  <si>
+    <t>Actively recruiting Product Engineers for web console and developer SDKs.</t>
+  </si>
+  <si>
+    <t>Glauber Costa</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/glbrc</t>
+  </si>
+  <si>
+    <t>https://turso.tech/careers</t>
+  </si>
+  <si>
+    <t>Build an offline sync demo using libSQL on mobile and message Glauber Costa</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide company. Heavy emphasis on database speed and developer simplicity. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L058</t>
   </si>
   <si>
+    <t>Upstash</t>
+  </si>
+  <si>
+    <t>https://upstash.com</t>
+  </si>
+  <si>
+    <t>Serverless data platform offering Redis, Kafka, and Vector search with per-request pricing.</t>
+  </si>
+  <si>
+    <t>Fast-growing serverless platform recruiting fullstack and developer experience engineers.</t>
+  </si>
+  <si>
+    <t>Enver Bisevac</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/enverbisevac</t>
+  </si>
+  <si>
+    <t>https://upstash.com/careers</t>
+  </si>
+  <si>
+    <t>Share Matinee Redis atomic hold benchmarks in outreach to Enver Bisevac</t>
+  </si>
+  <si>
+    <t>Worldwide remote team. Direct match with Redis caching and rate-limiting expertise. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L059</t>
   </si>
   <si>
+    <t>Drizzle Team</t>
+  </si>
+  <si>
+    <t>https://orm.drizzle.team</t>
+  </si>
+  <si>
+    <t>Next-generation TypeScript ORM that runs on any serverless or edge runtime.</t>
+  </si>
+  <si>
+    <t>Rapid adoption across TypeScript ecosystem; hires community maintainers and engineers.</t>
+  </si>
+  <si>
+    <t>Alex Blokh</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/alex-blokh</t>
+  </si>
+  <si>
+    <t>Review Drizzle schema migration tools and reach out on Discord/LinkedIn</t>
+  </si>
+  <si>
+    <t>Lean open-source team. Exceptional TypeScript typing and SQL generation. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L060</t>
   </si>
   <si>
+    <t>Prisma</t>
+  </si>
+  <si>
+    <t>https://prisma.io</t>
+  </si>
+  <si>
+    <t>Next-generation ORM and database developer platform for Node.js and TypeScript.</t>
+  </si>
+  <si>
+    <t>Recruiting for Prisma Studio, Prisma Accelerate, and Client engineering.</t>
+  </si>
+  <si>
+    <t>Johannes Schickling</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/schickling</t>
+  </si>
+  <si>
+    <t>https://prisma.io/careers</t>
+  </si>
+  <si>
+    <t>Highlight Prisma relational modeling from Rota and Matinee in application</t>
+  </si>
+  <si>
+    <t>Berlin HQ with worldwide remote team. High standard for developer tools. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L061</t>
   </si>
   <si>
+    <t>Paystack</t>
+  </si>
+  <si>
+    <t>https://paystack.com</t>
+  </si>
+  <si>
+    <t>Modern financial infrastructure and payment processing for commerce in Africa (Stripe co.).</t>
+  </si>
+  <si>
+    <t>Regularly recruits Product Engineers and Design Engineers for merchant dashboard and checkout.</t>
+  </si>
+  <si>
+    <t>Shola Akinlade</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/shola-akinlade</t>
+  </si>
+  <si>
+    <t>https://paystack.com/careers</t>
+  </si>
+  <si>
+    <t>Review Paystack React Native checkout SDK and draft message to Shola Akinlade</t>
+  </si>
+  <si>
+    <t>Lagos HQ / San Francisco. Remote-first African fintech with world-class engineering bar. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L062</t>
   </si>
   <si>
+    <t>Flutterwave</t>
+  </si>
+  <si>
+    <t>https://flutterwave.com</t>
+  </si>
+  <si>
+    <t>Global payment gateway and financial infrastructure empowering African businesses.</t>
+  </si>
+  <si>
+    <t>Hiring Product Engineers and Mobile Engineers for Send App and merchant platforms.</t>
+  </si>
+  <si>
+    <t>Olugbenga Agboola</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/gbolahan-olugbenga-agboola</t>
+  </si>
+  <si>
+    <t>https://flutterwave.com/careers</t>
+  </si>
+  <si>
+    <t>Reference Flutterwave webhook integration from Rota project in outreach</t>
+  </si>
+  <si>
+    <t>Global payments leader across Africa. High transaction volume and resilience focus. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L063</t>
   </si>
   <si>
+    <t>Mono</t>
+  </si>
+  <si>
+    <t>https://mono.co</t>
+  </si>
+  <si>
+    <t>Open banking and financial data infrastructure for African fintech and institutions.</t>
+  </si>
+  <si>
+    <t>Y Combinator fintech; recruits Product Engineers for DirectPay and Connect widget.</t>
+  </si>
+  <si>
+    <t>Abdulhamid Hassan</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/abdulhamidhassan</t>
+  </si>
+  <si>
+    <t>https://mono.co/careers</t>
+  </si>
+  <si>
+    <t>Inspect Mono Connect SDK and message Abdulhamid Hassan</t>
+  </si>
+  <si>
+    <t>High-growth open banking leader in Nigeria. Remote-friendly tech culture. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L064</t>
   </si>
   <si>
+    <t>Stitch</t>
+  </si>
+  <si>
+    <t>https://stitch.money</t>
+  </si>
+  <si>
+    <t>Payments infrastructure and automated reconciliation for enterprises across Africa.</t>
+  </si>
+  <si>
+    <t>Series A funding; hiring Product Engineers and integrations engineers.</t>
+  </si>
+  <si>
+    <t>Kiaan Pillay</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/kiaan-pillay-3617b738</t>
+  </si>
+  <si>
+    <t>https://stitch.money/careers</t>
+  </si>
+  <si>
+    <t>Draft outreach to Kiaan Pillay highlighting backend ledger and payment workflows</t>
+  </si>
+  <si>
+    <t>South Africa / Nigeria remote-friendly fintech platform. Strong engineering focus. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L065</t>
   </si>
   <si>
+    <t>Korapay</t>
+  </si>
+  <si>
+    <t>https://korapay.com</t>
+  </si>
+  <si>
+    <t>Cross-border payment infrastructure and payment engine for businesses operating across Africa.</t>
+  </si>
+  <si>
+    <t>Actively recruiting Product Engineers and Frontend Engineers for merchant solutions.</t>
+  </si>
+  <si>
+    <t>Dickson Nsofor</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/dicksonnsofor</t>
+  </si>
+  <si>
+    <t>https://korapay.com/careers</t>
+  </si>
+  <si>
+    <t>Prepare application showing fintech integration experience and message Dickson Nsofor</t>
+  </si>
+  <si>
+    <t>Lagos &amp; remote. Excellent payment reliability engineering track record. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L066</t>
   </si>
   <si>
+    <t>Piggyvest</t>
+  </si>
+  <si>
+    <t>https://piggyvest.com</t>
+  </si>
+  <si>
+    <t>Automated savings, micro-investment, and wealth management platform for millions of users.</t>
+  </si>
+  <si>
+    <t>Hiring Product Engineers and Mobile Engineers for consumer mobile products.</t>
+  </si>
+  <si>
+    <t>Somto Ifezue</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/somto-ifezue-66779147</t>
+  </si>
+  <si>
+    <t>https://piggyvest.com/careers</t>
+  </si>
+  <si>
+    <t>Highlight high-concurrency ticket reservations and state management from Matinee</t>
+  </si>
+  <si>
+    <t>Top tier consumer fintech in Nigeria. Mobile-first engineering team. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L067</t>
   </si>
   <si>
+    <t>Cowrywise</t>
+  </si>
+  <si>
+    <t>https://cowrywise.com</t>
+  </si>
+  <si>
+    <t>Digital wealth management and investment app providing mutual funds and automated savings.</t>
+  </si>
+  <si>
+    <t>Y Combinator startup hiring mobile and product engineers.</t>
+  </si>
+  <si>
+    <t>Razaq Ahmed</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/razaqahmed</t>
+  </si>
+  <si>
+    <t>https://cowrywise.com/careers</t>
+  </si>
+  <si>
+    <t>Reach out to Razaq Ahmed showing mobile React Native UI component mastery</t>
+  </si>
+  <si>
+    <t>Renowned for clean UI/UX and financial technology engineering in Africa. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L068</t>
   </si>
   <si>
+    <t>Chowdeck</t>
+  </si>
+  <si>
+    <t>https://chowdeck.com</t>
+  </si>
+  <si>
+    <t>On-demand food delivery, quick commerce, and dispatch logistics platform in Africa.</t>
+  </si>
+  <si>
+    <t>Y Combinator startup expanding logistics technology and rider/customer mobile apps.</t>
+  </si>
+  <si>
+    <t>Femi Aluko</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/femi-aluko</t>
+  </si>
+  <si>
+    <t>https://chowdeck.com/careers</t>
+  </si>
+  <si>
+    <t>Showcase mobile geolocation and order state management in pitch to Femi Aluko</t>
+  </si>
+  <si>
+    <t>Fastest-growing delivery app in Nigeria. High app performance standards. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L069</t>
   </si>
   <si>
+    <t>Termii</t>
+  </si>
+  <si>
+    <t>https://termii.com</t>
+  </si>
+  <si>
+    <t>Communications platform-as-a-service (CPaaS) providing SMS, voice, and OTP verification across Africa.</t>
+  </si>
+  <si>
+    <t>Expanding customer-facing dashboard and messaging routing APIs.</t>
+  </si>
+  <si>
+    <t>Emmanuel Gbolahan</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/gbolahanemmanuel</t>
+  </si>
+  <si>
+    <t>https://termii.com/careers</t>
+  </si>
+  <si>
+    <t>Highlight multi-channel notifications and queue processing from Background Job System</t>
+  </si>
+  <si>
+    <t>Y Combinator alumnus. The Twilio of Africa; reliable messaging infrastructure. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L070</t>
   </si>
   <si>
+    <t>Sendchamp</t>
+  </si>
+  <si>
+    <t>https://sendchamp.com</t>
+  </si>
+  <si>
+    <t>Omnichannel messaging platform for African businesses (SMS, WhatsApp, Email, Voice).</t>
+  </si>
+  <si>
+    <t>Recruits Product Engineers to build developer SDKs and campaign builders.</t>
+  </si>
+  <si>
+    <t>Goodness Kayode</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/goodnesskayode</t>
+  </si>
+  <si>
+    <t>https://sendchamp.com/careers</t>
+  </si>
+  <si>
+    <t>Draft message to Goodness Kayode demonstrating async queue architecture</t>
+  </si>
+  <si>
+    <t>Developer-focused messaging infrastructure. Acquired by OneLiquidity. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L071</t>
   </si>
   <si>
+    <t>WorkOS</t>
+  </si>
+  <si>
+    <t>https://workos.com</t>
+  </si>
+  <si>
+    <t>Enterprise-ready APIs for Single Sign-On (SAML), Directory Sync (SCIM), and audit logs.</t>
+  </si>
+  <si>
+    <t>Actively recruiting Product Engineers and Design Engineers for developer portal.</t>
+  </si>
+  <si>
+    <t>Michael Grinich</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/michaelgrinich</t>
+  </si>
+  <si>
+    <t>https://workos.com/careers</t>
+  </si>
+  <si>
+    <t>Review WorkOS Admin Portal and message Michael Grinich with UX observations</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide. High bar for developer documentation and interface polish. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L072</t>
   </si>
   <si>
+    <t>Stytch</t>
+  </si>
+  <si>
+    <t>https://stytch.com</t>
+  </si>
+  <si>
+    <t>Developer platform for passwordless authentication, biometrics, and B2B SaaS auth.</t>
+  </si>
+  <si>
+    <t>Regularly posts product and frontend engineering openings on Ashby.</t>
+  </si>
+  <si>
+    <t>Reed McGinley-Stempel</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/reed-mcginley-stempel</t>
+  </si>
+  <si>
+    <t>https://stytch.com/careers</t>
+  </si>
+  <si>
+    <t>Draft note to Reed McGinley-Stempel highlighting JWT security model from Rota</t>
+  </si>
+  <si>
+    <t>Benchmark authentication developer platform. Strong remote hiring culture. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L073</t>
   </si>
   <si>
+    <t>Svix</t>
+  </si>
+  <si>
+    <t>https://svix.com</t>
+  </si>
+  <si>
+    <t>Webhooks as a service platform providing webhooks sending, receiving, and verification.</t>
+  </si>
+  <si>
+    <t>Y Combinator company; recruits Product Engineers to build webhook dashboard.</t>
+  </si>
+  <si>
+    <t>Tom Hacohen</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tomhacohen</t>
+  </si>
+  <si>
+    <t>https://svix.com/careers</t>
+  </si>
+  <si>
+    <t>Highlight webhook idempotency and signature verification experience in pitch to Tom Hacohen</t>
+  </si>
+  <si>
+    <t>Remote-first worldwide. High overlap with distributed event processing and retry logic. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L074</t>
   </si>
   <si>
+    <t>Convoy</t>
+  </si>
+  <si>
+    <t>https://getconvoy.io</t>
+  </si>
+  <si>
+    <t>Cloud-native webhooks gateway for publishing, receiving, and monitoring webhooks.</t>
+  </si>
+  <si>
+    <t>Open-source webhooks platform founded in Nigeria; hires remote fullstack engineers.</t>
+  </si>
+  <si>
+    <t>Subomi Plumptre</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/subomiplumptre</t>
+  </si>
+  <si>
+    <t>https://getconvoy.io/careers</t>
+  </si>
+  <si>
+    <t>Explore Convoy GitHub repository and share feedback with engineering team</t>
+  </si>
+  <si>
+    <t>Open-source webhook infrastructure with active worldwide community. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L075</t>
   </si>
   <si>
+    <t>Customer.io</t>
+  </si>
+  <si>
+    <t>https://customer.io</t>
+  </si>
+  <si>
+    <t>Automated messaging and customer data platform for modern tech enterprises.</t>
+  </si>
+  <si>
+    <t>Remote-first pioneer; frequently recruits Product Engineers across the globe.</t>
+  </si>
+  <si>
+    <t>Colin Nederkoorn</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/colinnederkoorn</t>
+  </si>
+  <si>
+    <t>https://customer.io/careers</t>
+  </si>
+  <si>
+    <t>Review Customer.io journey builder UI and send pitch to engineering hiring leads</t>
+  </si>
+  <si>
+    <t>100% remote worldwide team with transparent culture and competitive pay. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L076</t>
   </si>
   <si>
+    <t>OneSignal</t>
+  </si>
+  <si>
+    <t>https://onesignal.com</t>
+  </si>
+  <si>
+    <t>Omnichannel customer engagement engine sending billions of push notifications and emails daily.</t>
+  </si>
+  <si>
+    <t>Actively recruiting Product Engineers for mobile SDKs and campaign dashboard.</t>
+  </si>
+  <si>
+    <t>George Deglin</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/georgedeglin</t>
+  </si>
+  <si>
+    <t>https://onesignal.com/careers</t>
+  </si>
+  <si>
+    <t>Reference push notification queue architecture in message to George Deglin</t>
+  </si>
+  <si>
+    <t>Market-leading notification infrastructure. High concurrency and scalability focus. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L077</t>
   </si>
   <si>
+    <t>LinearB</t>
+  </si>
+  <si>
+    <t>https://linearb.io</t>
+  </si>
+  <si>
+    <t>Software delivery intelligence platform optimizing engineering team metrics and pull requests.</t>
+  </si>
+  <si>
+    <t>Hiring remote Product Engineers to build developer metrics dashboards and git automations.</t>
+  </si>
+  <si>
+    <t>Ori Keren</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/orikeren</t>
+  </si>
+  <si>
+    <t>https://linearb.io/careers</t>
+  </si>
+  <si>
+    <t>Connect with LinearB engineering team on LinkedIn with insights on developer workflow tracking</t>
+  </si>
+  <si>
+    <t>Global remote-friendly engineering culture. Focuses on DORA metrics and Git workflow. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L078</t>
   </si>
   <si>
+    <t>Swimm</t>
+  </si>
+  <si>
+    <t>https://swimm.io</t>
+  </si>
+  <si>
+    <t>Continuous codebase documentation platform that automatically updates alongside code changes.</t>
+  </si>
+  <si>
+    <t>Recruiting Product Engineers and Design Engineers for IDE plugins and web app.</t>
+  </si>
+  <si>
+    <t>Oren Toledano</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/orentoledano</t>
+  </si>
+  <si>
+    <t>https://swimm.io/careers</t>
+  </si>
+  <si>
+    <t>Document an open-source project with Swimm and message Oren Toledano</t>
+  </si>
+  <si>
+    <t>Developer documentation coupled directly to Git commits. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L079</t>
   </si>
   <si>
+    <t>Kinde</t>
+  </si>
+  <si>
+    <t>https://kinde.com</t>
+  </si>
+  <si>
+    <t>Simple, powerful authentication, authorization, and feature flagging platform for SaaS.</t>
+  </si>
+  <si>
+    <t>Australian / global remote startup; hiring Product Engineers for developer platform.</t>
+  </si>
+  <si>
+    <t>Ross Chaldecott</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/rosschaldecott</t>
+  </si>
+  <si>
+    <t>https://kinde.com/careers</t>
+  </si>
+  <si>
+    <t>Review Kinde Next.js SDK and draft tailored note to Ross Chaldecott</t>
+  </si>
+  <si>
+    <t>High visual craft and simplicity in authentication and user billing. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L080</t>
   </si>
   <si>
+    <t>Andela</t>
+  </si>
+  <si>
+    <t>https://andela.com</t>
+  </si>
+  <si>
+    <t>Global talent network matching vetted software engineers with global enterprises.</t>
+  </si>
+  <si>
+    <t>Continuous hiring for Product Engineers and Fullstack Engineers across distributed client projects.</t>
+  </si>
+  <si>
+    <t>Carrol Chang</t>
+  </si>
+  <si>
+    <t>CEO</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/carrolchang</t>
+  </si>
+  <si>
+    <t>https://andela.com/careers</t>
+  </si>
+  <si>
+    <t>Submit verified profile to Andela talent network highlighting Rota and Matinee apps</t>
+  </si>
+  <si>
+    <t>Extensive track record placing African engineering talent with global remote employers. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L081</t>
   </si>
   <si>
+    <t>Cognition</t>
+  </si>
+  <si>
+    <t>https://cognition.ai</t>
+  </si>
+  <si>
+    <t>Applied AI lab building Devin, the first autonomous AI software development agent.</t>
+  </si>
+  <si>
+    <t>Actively recruiting foundational Product Engineers to build user interfaces and sandboxes.</t>
+  </si>
+  <si>
+    <t>Scott Wu</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/scottwu1</t>
+  </si>
+  <si>
+    <t>https://cognition.ai/careers</t>
+  </si>
+  <si>
+    <t>Draft message to Scott Wu highlighting background in agentic coding workflows and terminal execution</t>
+  </si>
+  <si>
+    <t>Frontier AI engineering organization. Extremely high technical bar. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L082</t>
   </si>
   <si>
+    <t>Replit</t>
+  </si>
+  <si>
+    <t>https://replit.com</t>
+  </si>
+  <si>
+    <t>Collaborative cloud software development environment and AI-assisted deployment platform.</t>
+  </si>
+  <si>
+    <t>Hiring Product Engineers for Replit Agent and mobile coding applications.</t>
+  </si>
+  <si>
+    <t>Amjad Masad</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/amjadmasad</t>
+  </si>
+  <si>
+    <t>https://replit.com/careers</t>
+  </si>
+  <si>
+    <t>Build and deploy a mobile template on Replit and share with Amjad Masad</t>
+  </si>
+  <si>
+    <t>Global remote-friendly software development community. Millions of builders. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L083</t>
   </si>
   <si>
+    <t>Diagram</t>
+  </si>
+  <si>
+    <t>https://diagram.com</t>
+  </si>
+  <si>
+    <t>Design technology lab building AI-native UI design and generation tools (now part of Figma).</t>
+  </si>
+  <si>
+    <t>Pioneered AI design tools (Magician, Genius); influential in design engineering.</t>
+  </si>
+  <si>
+    <t>Jordan Singer</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ibuildmyideas</t>
+  </si>
+  <si>
+    <t>Prepare a prototype demonstration of generative UI components and reach out to Jordan Singer</t>
+  </si>
+  <si>
+    <t>The gold standard for Design Engineering and generative UI tools. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L084</t>
   </si>
   <si>
+    <t>Cursor (Anysphere)</t>
+  </si>
+  <si>
+    <t>https://cursor.com</t>
+  </si>
+  <si>
+    <t>AI-first code editor built for hyper-productive pair programming and codebase generation.</t>
+  </si>
+  <si>
+    <t>Rapidly expanding product engineering team for editor UX, extensions, and agent flows.</t>
+  </si>
+  <si>
+    <t>Michael Truell</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/michaeltruell</t>
+  </si>
+  <si>
+    <t>https://cursor.com/careers</t>
+  </si>
+  <si>
+    <t>Document daily experience with agentic coding tools in pitch to Michael Truell</t>
+  </si>
+  <si>
+    <t>The preeminent AI code editor. Values speed, clean UI, and deep developer empathy. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L085</t>
   </si>
   <si>
+    <t>Revelo</t>
+  </si>
+  <si>
+    <t>https://revelo.com</t>
+  </si>
+  <si>
+    <t>Global talent platform connecting remote software engineers with high-growth US tech companies.</t>
+  </si>
+  <si>
+    <t>Continuously sourcing Product Engineers and Mobile Engineers for US client placements.</t>
+  </si>
+  <si>
+    <t>Lucas Mendes</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/lucas-mendes-revelo</t>
+  </si>
+  <si>
+    <t>https://revelo.com/careers</t>
+  </si>
+  <si>
+    <t>Register on Revelo platform and highlight Rota and Matinee case studies</t>
+  </si>
+  <si>
+    <t>Strong EOR infrastructure supporting full-time remote international employment. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L086</t>
   </si>
   <si>
+    <t>Braintrust</t>
+  </si>
+  <si>
+    <t>https://usebraintrust.com</t>
+  </si>
+  <si>
+    <t>Decentralized talent network connecting top freelance and remote engineers with Fortune 500 enterprises.</t>
+  </si>
+  <si>
+    <t>Active hiring boards for mobile engineers (React Native) and full-stack product engineers.</t>
+  </si>
+  <si>
+    <t>Adam Jackson</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/adamjackson</t>
+  </si>
+  <si>
+    <t>https://usebraintrust.com/careers</t>
+  </si>
+  <si>
+    <t>Complete Braintrust profile verification showcasing verified load test benchmarks</t>
+  </si>
+  <si>
+    <t>No middleman fee model for talent; global remote contractor opportunities. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L087</t>
   </si>
   <si>
+    <t>Toptal</t>
+  </si>
+  <si>
+    <t>https://toptal.com</t>
+  </si>
+  <si>
+    <t>Exclusive global network of freelance software engineers, designers, and finance experts.</t>
+  </si>
+  <si>
+    <t>Continuous inbound client demand for React Native and TypeScript product engineers.</t>
+  </si>
+  <si>
+    <t>Taso Du Val</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tasoduval</t>
+  </si>
+  <si>
+    <t>https://toptal.com/careers</t>
+  </si>
+  <si>
+    <t>Initiate Toptal technical screening with Rota and Matinee architecture portfolio</t>
+  </si>
+  <si>
+    <t>Global remote network with high compensation rates for verified engineers. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L088</t>
   </si>
   <si>
+    <t>Turing</t>
+  </si>
+  <si>
+    <t>https://turing.com</t>
+  </si>
+  <si>
+    <t>AI-powered talent cloud matching pre-vetted remote software engineers with Silicon Valley tech firms.</t>
+  </si>
+  <si>
+    <t>High demand for mobile product engineers with React Native, Node.js, and Redis skills.</t>
+  </si>
+  <si>
+    <t>Jonathan Siddharth</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/jonathansiddharth</t>
+  </si>
+  <si>
+    <t>https://turing.com/careers</t>
+  </si>
+  <si>
+    <t>Complete Turing automated technical assessment highlighting TypeScript backend expertise</t>
+  </si>
+  <si>
+    <t>Fully remote workforce covering 150+ countries. Direct salary payment in USD. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L089</t>
   </si>
   <si>
+    <t>Eden Life</t>
+  </si>
+  <si>
+    <t>https://oureveryday.life</t>
+  </si>
+  <si>
+    <t>Tech-enabled home concierge and automated home services platform operating in Lagos and Nairobi.</t>
+  </si>
+  <si>
+    <t>Product-led African startup; recruits Product Engineers to build mobile apps and operations tools.</t>
+  </si>
+  <si>
+    <t>Nadayar Enegesi</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/nadayarenegesi</t>
+  </si>
+  <si>
+    <t>https://oureveryday.life/careers</t>
+  </si>
+  <si>
+    <t>Message Nadayar Enegesi referencing Rota shift-swap logistics model</t>
+  </si>
+  <si>
+    <t>Founded by Andela co-founder Nadayar Enegesi. Superb product engineering and consumer UX focus. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L090</t>
   </si>
   <si>
+    <t>Brass</t>
+  </si>
+  <si>
+    <t>https://trybrass.com</t>
+  </si>
+  <si>
+    <t>Digital business banking and financial operations platform for African startups and SMBs.</t>
+  </si>
+  <si>
+    <t>Modern fintech recruiting Product Engineers for business accounts and expense cards.</t>
+  </si>
+  <si>
+    <t>Sola Akindolu</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/solaakindolu</t>
+  </si>
+  <si>
+    <t>https://trybrass.com/careers</t>
+  </si>
+  <si>
+    <t>Review Brass corporate dashboard features and draft note to Sola Akindolu</t>
+  </si>
+  <si>
+    <t>Lagos &amp; remote. Backed by Ventures Platform. Clean financial software interfaces. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L091</t>
   </si>
   <si>
+    <t>Remedial Health</t>
+  </si>
+  <si>
+    <t>https://remedialhealth.com</t>
+  </si>
+  <si>
+    <t>Digital procurement, inventory management, and financing platform for pharmacies in Africa.</t>
+  </si>
+  <si>
+    <t>Y Combinator startup hiring mobile and product engineers to digitize health supply chains.</t>
+  </si>
+  <si>
+    <t>Samuel Okwuada</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/samuelokwuada</t>
+  </si>
+  <si>
+    <t>https://remedialhealth.com/careers</t>
+  </si>
+  <si>
+    <t>Draft application demonstrating mobile offline sync capabilities from Rota</t>
+  </si>
+  <si>
+    <t>High-impact B2B healthtech. Operates across major Nigerian pharmaceutical supply chains. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L092</t>
   </si>
   <si>
+    <t>Helicarrier</t>
+  </si>
+  <si>
+    <t>https://helicarrier.studio</t>
+  </si>
+  <si>
+    <t>Cryptocurrency infrastructure and cross-border money transfer software for Africa (Sendcash).</t>
+  </si>
+  <si>
+    <t>Product-driven engineering team; hires engineers passionate about borderless digital payments.</t>
+  </si>
+  <si>
+    <t>Timi Ajiboye</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/timi-ajiboye</t>
+  </si>
+  <si>
+    <t>Connect with Timi Ajiboye showing fullstack Web3 and financial transaction experience</t>
+  </si>
+  <si>
+    <t>Pioneered crypto infrastructure in Nigeria. Exceptional engineering culture. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L093</t>
   </si>
   <si>
+    <t>SurrealDB</t>
+  </si>
+  <si>
+    <t>https://surrealdb.com</t>
+  </si>
+  <si>
+    <t>Ultimate multi-model database for web, cloud, and edge applications.</t>
+  </si>
+  <si>
+    <t>High GitHub momentum; recruits Product Engineers to build web studio and cloud dashboard.</t>
+  </si>
+  <si>
+    <t>Tobie Morgan Hitchcock</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/tobiemorganhitchcock</t>
+  </si>
+  <si>
+    <t>https://surrealdb.com/careers</t>
+  </si>
+  <si>
+    <t>Test SurrealDB web console and message Tobie Hitchcock with observations</t>
+  </si>
+  <si>
+    <t>Remote-first global company. Massive developer interest in multi-model database capabilities. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L094</t>
   </si>
   <si>
+    <t>PocketBase</t>
+  </si>
+  <si>
+    <t>https://pocketbase.io</t>
+  </si>
+  <si>
+    <t>Open-source Go/SQLite backend-as-a-service embedded in a single portable file.</t>
+  </si>
+  <si>
+    <t>Top trending open-source backend tool; recruits community contributors and UI builders.</t>
+  </si>
+  <si>
+    <t>Gani Georgiev</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ganigeorgiev</t>
+  </si>
+  <si>
+    <t>Submit a documentation improvement to PocketBase on GitHub before outreach</t>
+  </si>
+  <si>
+    <t>Lean open-source software with massive worldwide adoption. SQLite and Go architecture. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L095</t>
   </si>
   <si>
+    <t>Saleor</t>
+  </si>
+  <si>
+    <t>https://saleor.io</t>
+  </si>
+  <si>
+    <t>Headless, GraphQL-first enterprise e-commerce platform built on Python and Next.js.</t>
+  </si>
+  <si>
+    <t>Actively recruiting frontend and product engineers for Saleor Dashboard and Cloud.</t>
+  </si>
+  <si>
+    <t>Mirek Zimnoch</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/mirekzimnoch</t>
+  </si>
+  <si>
+    <t>https://saleor.io/careers</t>
+  </si>
+  <si>
+    <t>Inspect Saleor Next.js commerce storefront template and reach out to Mirek Zimnoch</t>
+  </si>
+  <si>
+    <t>Global remote team with Europe roots. High GraphQL and TypeScript component standards. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L096</t>
   </si>
   <si>
+    <t>Strapi</t>
+  </si>
+  <si>
+    <t>https://strapi.io</t>
+  </si>
+  <si>
+    <t>Leading open-source headless CMS enabling developers to build customizable APIs in JavaScript.</t>
+  </si>
+  <si>
+    <t>Continuous hiring for Product Engineers, Design Engineers, and developer relations.</t>
+  </si>
+  <si>
+    <t>Aurélien Georget</t>
+  </si>
+  <si>
+    <t>CPO</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/aureliengeorget</t>
+  </si>
+  <si>
+    <t>https://strapi.io/careers</t>
+  </si>
+  <si>
+    <t>Highlight experience with Node.js REST API architectures in pitch to Aurélien Georget</t>
+  </si>
+  <si>
+    <t>Remote-first global company. Used by millions of developers for custom content APIs. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L097</t>
   </si>
   <si>
+    <t>Courier</t>
+  </si>
+  <si>
+    <t>https://courier.com</t>
+  </si>
+  <si>
+    <t>Developer notification platform for design, routing, and delivery across push, SMS, email, and Slack.</t>
+  </si>
+  <si>
+    <t>Recruiting remote Product Engineers to build notification workflow builder.</t>
+  </si>
+  <si>
+    <t>Troy Goode</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/troygoode</t>
+  </si>
+  <si>
+    <t>https://courier.com/careers</t>
+  </si>
+  <si>
+    <t>Review Courier notification builder and reach out to Troy Goode</t>
+  </si>
+  <si>
+    <t>Y Combinator alumnus. Remote-first worldwide hiring. Deep relevance to notification system design. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L098</t>
   </si>
   <si>
+    <t>LinearB (DevOps Intelligence)</t>
+  </si>
+  <si>
+    <t>Engineering effectiveness and Git analytics platform automating code review pipelines.</t>
+  </si>
+  <si>
+    <t>Series B tech platform scaling Product Engineering team.</t>
+  </si>
+  <si>
+    <t>Dan Lines</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/danlines</t>
+  </si>
+  <si>
+    <t>Draft message to Dan Lines highlighting engineering decision logs and ADR practices</t>
+  </si>
+  <si>
+    <t>Focuses on developer workflow optimization and PR velocity. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L099</t>
   </si>
   <si>
+    <t>Chipper Cash</t>
+  </si>
+  <si>
+    <t>https://chippercash.com</t>
+  </si>
+  <si>
+    <t>Cross-border peer-to-peer payments, virtual visa cards, and investment app across Africa.</t>
+  </si>
+  <si>
+    <t>Hiring Product Engineers and Mobile Engineers for high-volume consumer payment flows.</t>
+  </si>
+  <si>
+    <t>Ham Serunjogi</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ham-serunjogi</t>
+  </si>
+  <si>
+    <t>https://chippercash.com/careers</t>
+  </si>
+  <si>
+    <t>Prepare pitch to Ham Serunjogi highlighting mobile concurrency and transaction integrity</t>
+  </si>
+  <si>
+    <t>Over 5 million users across Africa and the diaspora. Mobile-first engineering architecture. Checked 19 Oct 2026.</t>
+  </si>
+  <si>
     <t>L100</t>
+  </si>
+  <si>
+    <t>Codesee</t>
+  </si>
+  <si>
+    <t>https://codesee.io</t>
+  </si>
+  <si>
+    <t>Continuous code understanding and codebase visualization platform for engineering teams.</t>
+  </si>
+  <si>
+    <t>Techstars/venture-backed remote startup hiring developer experience and product engineers.</t>
+  </si>
+  <si>
+    <t>Shanea Leven</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/shanealeven</t>
+  </si>
+  <si>
+    <t>https://codesee.io/careers</t>
+  </si>
+  <si>
+    <t>Draft message to Shanea Leven highlighting complex distributed architecture modeling</t>
+  </si>
+  <si>
+    <t>100% remote-first company. Visualizing code dependencies and architecture changes. Checked 19 Oct 2026.</t>
   </si>
   <si>
     <t>Date</t>
@@ -2767,2001 +4918,4881 @@
       <c r="A22" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="B22" s="3"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
+      <c r="B22" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O22" s="3"/>
-      <c r="P22" s="2"/>
+      <c r="P22" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q22" s="3"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="4"/>
-      <c r="T22" s="3"/>
-      <c r="U22" s="4"/>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="T22" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
+        <v>238</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O23" s="3"/>
-      <c r="P23" s="2"/>
+      <c r="P23" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q23" s="3"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="4"/>
-      <c r="T23" s="3"/>
-      <c r="U23" s="4"/>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="T23" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="B24" s="3"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O24" s="3"/>
-      <c r="P24" s="2"/>
+      <c r="P24" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q24" s="3"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="3"/>
-      <c r="U24" s="4"/>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="T24" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
+        <v>258</v>
+      </c>
+      <c r="B25" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="K25" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N25" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O25" s="3"/>
-      <c r="P25" s="2"/>
+      <c r="P25" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q25" s="3"/>
-      <c r="R25" s="2"/>
-      <c r="S25" s="4"/>
-      <c r="T25" s="3"/>
-      <c r="U25" s="4"/>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="T25" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="B26" s="3"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
+        <v>268</v>
+      </c>
+      <c r="B26" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H26" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M26" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N26" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O26" s="3"/>
-      <c r="P26" s="2"/>
+      <c r="P26" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q26" s="3"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="4"/>
-      <c r="T26" s="3"/>
-      <c r="U26" s="4"/>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
+      <c r="S26" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="T26" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="4"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="4"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="B27" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N27" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O27" s="3"/>
-      <c r="P27" s="2"/>
+      <c r="P27" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q27" s="3"/>
-      <c r="R27" s="2"/>
-      <c r="S27" s="4"/>
-      <c r="T27" s="3"/>
-      <c r="U27" s="4"/>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
+      <c r="S27" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="T27" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B28" s="3"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="4"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="4"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
+        <v>288</v>
+      </c>
+      <c r="B28" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M28" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N28" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O28" s="3"/>
-      <c r="P28" s="2"/>
+      <c r="P28" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q28" s="3"/>
-      <c r="R28" s="2"/>
-      <c r="S28" s="4"/>
-      <c r="T28" s="3"/>
-      <c r="U28" s="4"/>
+      <c r="R28" s="2">
+        <v>0</v>
+      </c>
+      <c r="S28" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="T28" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U28" s="4" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="4"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="4"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
+        <v>298</v>
+      </c>
+      <c r="B29" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>301</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>304</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M29" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N29" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O29" s="3"/>
-      <c r="P29" s="2"/>
+      <c r="P29" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q29" s="3"/>
-      <c r="R29" s="2"/>
-      <c r="S29" s="4"/>
-      <c r="T29" s="3"/>
-      <c r="U29" s="4"/>
+      <c r="R29" s="2">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4" t="s">
+        <v>306</v>
+      </c>
+      <c r="T29" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>307</v>
+      </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="4"/>
-      <c r="I30" s="2"/>
-      <c r="J30" s="4"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
-      <c r="N30" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="B30" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M30" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N30" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O30" s="3"/>
-      <c r="P30" s="2"/>
+      <c r="P30" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q30" s="3"/>
-      <c r="R30" s="2"/>
-      <c r="S30" s="4"/>
-      <c r="T30" s="3"/>
-      <c r="U30" s="4"/>
+      <c r="R30" s="2">
+        <v>0</v>
+      </c>
+      <c r="S30" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="T30" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
-      <c r="N31" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="B31" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>322</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M31" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N31" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O31" s="3"/>
-      <c r="P31" s="2"/>
+      <c r="P31" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q31" s="3"/>
-      <c r="R31" s="2"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="3"/>
-      <c r="U31" s="4"/>
+      <c r="R31" s="2">
+        <v>0</v>
+      </c>
+      <c r="S31" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="T31" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="B32" s="3"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="2"/>
-      <c r="M32" s="2"/>
-      <c r="N32" s="2"/>
+        <v>329</v>
+      </c>
+      <c r="B32" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>330</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>331</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>333</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H32" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M32" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N32" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O32" s="3"/>
-      <c r="P32" s="2"/>
+      <c r="P32" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q32" s="3"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="3"/>
-      <c r="U32" s="4"/>
+      <c r="R32" s="2">
+        <v>0</v>
+      </c>
+      <c r="S32" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="T32" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="2"/>
-      <c r="M33" s="2"/>
-      <c r="N33" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="B33" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M33" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N33" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O33" s="3"/>
-      <c r="P33" s="2"/>
+      <c r="P33" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q33" s="3"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="3"/>
-      <c r="U33" s="4"/>
+      <c r="R33" s="2">
+        <v>0</v>
+      </c>
+      <c r="S33" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="T33" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U33" s="4" t="s">
+        <v>348</v>
+      </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="B34" s="3"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="2"/>
-      <c r="M34" s="2"/>
-      <c r="N34" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="B34" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M34" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N34" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O34" s="3"/>
-      <c r="P34" s="2"/>
+      <c r="P34" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q34" s="3"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="3"/>
-      <c r="U34" s="4"/>
+      <c r="R34" s="2">
+        <v>0</v>
+      </c>
+      <c r="S34" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="T34" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U34" s="4" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="2"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="2"/>
-      <c r="M35" s="2"/>
-      <c r="N35" s="2"/>
+        <v>359</v>
+      </c>
+      <c r="B35" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M35" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N35" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O35" s="3"/>
-      <c r="P35" s="2"/>
+      <c r="P35" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q35" s="3"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="3"/>
-      <c r="U35" s="4"/>
+      <c r="R35" s="2">
+        <v>0</v>
+      </c>
+      <c r="S35" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="T35" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U35" s="4" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="B36" s="3"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="2"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="2"/>
-      <c r="M36" s="2"/>
-      <c r="N36" s="2"/>
+        <v>369</v>
+      </c>
+      <c r="B36" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M36" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N36" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O36" s="3"/>
-      <c r="P36" s="2"/>
+      <c r="P36" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q36" s="3"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="3"/>
-      <c r="U36" s="4"/>
+      <c r="R36" s="2">
+        <v>0</v>
+      </c>
+      <c r="S36" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="T36" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U36" s="4" t="s">
+        <v>378</v>
+      </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="2"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="2"/>
-      <c r="M37" s="2"/>
-      <c r="N37" s="2"/>
+        <v>379</v>
+      </c>
+      <c r="B37" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M37" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N37" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O37" s="3"/>
-      <c r="P37" s="2"/>
+      <c r="P37" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q37" s="3"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="4"/>
-      <c r="T37" s="3"/>
-      <c r="U37" s="4"/>
+      <c r="R37" s="2">
+        <v>0</v>
+      </c>
+      <c r="S37" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="T37" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U37" s="4" t="s">
+        <v>388</v>
+      </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B38" s="3"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="2"/>
-      <c r="H38" s="4"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="4"/>
-      <c r="K38" s="4"/>
-      <c r="L38" s="2"/>
-      <c r="M38" s="2"/>
-      <c r="N38" s="2"/>
+        <v>389</v>
+      </c>
+      <c r="B38" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>393</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M38" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N38" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O38" s="3"/>
-      <c r="P38" s="2"/>
+      <c r="P38" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q38" s="3"/>
-      <c r="R38" s="2"/>
-      <c r="S38" s="4"/>
-      <c r="T38" s="3"/>
-      <c r="U38" s="4"/>
+      <c r="R38" s="2">
+        <v>0</v>
+      </c>
+      <c r="S38" s="4" t="s">
+        <v>397</v>
+      </c>
+      <c r="T38" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U38" s="4" t="s">
+        <v>398</v>
+      </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="2"/>
-      <c r="H39" s="4"/>
-      <c r="I39" s="2"/>
-      <c r="J39" s="4"/>
-      <c r="K39" s="4"/>
-      <c r="L39" s="2"/>
-      <c r="M39" s="2"/>
-      <c r="N39" s="2"/>
+        <v>399</v>
+      </c>
+      <c r="B39" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>403</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M39" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N39" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O39" s="3"/>
-      <c r="P39" s="2"/>
+      <c r="P39" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q39" s="3"/>
-      <c r="R39" s="2"/>
-      <c r="S39" s="4"/>
-      <c r="T39" s="3"/>
-      <c r="U39" s="4"/>
+      <c r="R39" s="2">
+        <v>0</v>
+      </c>
+      <c r="S39" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="T39" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>408</v>
+      </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="B40" s="3"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="2"/>
-      <c r="H40" s="4"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="4"/>
-      <c r="K40" s="4"/>
-      <c r="L40" s="2"/>
-      <c r="M40" s="2"/>
-      <c r="N40" s="2"/>
+        <v>409</v>
+      </c>
+      <c r="B40" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>410</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>411</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>412</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>414</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>415</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N40" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O40" s="3"/>
-      <c r="P40" s="2"/>
+      <c r="P40" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q40" s="3"/>
-      <c r="R40" s="2"/>
-      <c r="S40" s="4"/>
-      <c r="T40" s="3"/>
-      <c r="U40" s="4"/>
+      <c r="R40" s="2">
+        <v>0</v>
+      </c>
+      <c r="S40" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="T40" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U40" s="4" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="B41" s="3"/>
-      <c r="C41" s="4"/>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
-      <c r="G41" s="2"/>
-      <c r="H41" s="4"/>
-      <c r="I41" s="2"/>
-      <c r="J41" s="4"/>
-      <c r="K41" s="4"/>
-      <c r="L41" s="2"/>
-      <c r="M41" s="2"/>
-      <c r="N41" s="2"/>
+        <v>419</v>
+      </c>
+      <c r="B41" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>422</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M41" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O41" s="3"/>
-      <c r="P41" s="2"/>
+      <c r="P41" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q41" s="3"/>
-      <c r="R41" s="2"/>
-      <c r="S41" s="4"/>
-      <c r="T41" s="3"/>
-      <c r="U41" s="4"/>
+      <c r="R41" s="2">
+        <v>0</v>
+      </c>
+      <c r="S41" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="T41" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="B42" s="3"/>
-      <c r="C42" s="4"/>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
-      <c r="G42" s="2"/>
-      <c r="H42" s="4"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="4"/>
-      <c r="K42" s="4"/>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2"/>
+        <v>429</v>
+      </c>
+      <c r="B42" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>431</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M42" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N42" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O42" s="3"/>
-      <c r="P42" s="2"/>
+      <c r="P42" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q42" s="3"/>
-      <c r="R42" s="2"/>
-      <c r="S42" s="4"/>
-      <c r="T42" s="3"/>
-      <c r="U42" s="4"/>
+      <c r="R42" s="2">
+        <v>0</v>
+      </c>
+      <c r="S42" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="T42" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U42" s="4" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="B43" s="3"/>
-      <c r="C43" s="4"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
-      <c r="N43" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="B43" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>442</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="L43" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M43" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N43" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O43" s="3"/>
-      <c r="P43" s="2"/>
+      <c r="P43" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q43" s="3"/>
-      <c r="R43" s="2"/>
-      <c r="S43" s="4"/>
-      <c r="T43" s="3"/>
-      <c r="U43" s="4"/>
+      <c r="R43" s="2">
+        <v>0</v>
+      </c>
+      <c r="S43" s="4" t="s">
+        <v>447</v>
+      </c>
+      <c r="T43" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
-      <c r="N44" s="2"/>
+        <v>449</v>
+      </c>
+      <c r="B44" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>452</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="L44" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M44" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N44" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O44" s="3"/>
-      <c r="P44" s="2"/>
+      <c r="P44" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q44" s="3"/>
-      <c r="R44" s="2"/>
-      <c r="S44" s="4"/>
-      <c r="T44" s="3"/>
-      <c r="U44" s="4"/>
+      <c r="R44" s="2">
+        <v>0</v>
+      </c>
+      <c r="S44" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="T44" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="4"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="B45" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="E45" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>463</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="L45" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M45" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O45" s="3"/>
-      <c r="P45" s="2"/>
+      <c r="P45" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q45" s="3"/>
-      <c r="R45" s="2"/>
-      <c r="S45" s="4"/>
-      <c r="T45" s="3"/>
-      <c r="U45" s="4"/>
+      <c r="R45" s="2">
+        <v>0</v>
+      </c>
+      <c r="S45" s="4" t="s">
+        <v>467</v>
+      </c>
+      <c r="T45" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U45" s="4" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
-      <c r="N46" s="2"/>
+        <v>469</v>
+      </c>
+      <c r="B46" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H46" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="L46" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M46" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N46" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O46" s="3"/>
-      <c r="P46" s="2"/>
+      <c r="P46" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q46" s="3"/>
-      <c r="R46" s="2"/>
-      <c r="S46" s="4"/>
-      <c r="T46" s="3"/>
-      <c r="U46" s="4"/>
+      <c r="R46" s="2">
+        <v>0</v>
+      </c>
+      <c r="S46" s="4" t="s">
+        <v>477</v>
+      </c>
+      <c r="T46" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U46" s="4" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="4"/>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="4"/>
-      <c r="I47" s="2"/>
-      <c r="J47" s="4"/>
-      <c r="K47" s="4"/>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
-      <c r="N47" s="2"/>
+        <v>479</v>
+      </c>
+      <c r="B47" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H47" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O47" s="3"/>
-      <c r="P47" s="2"/>
+      <c r="P47" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q47" s="3"/>
-      <c r="R47" s="2"/>
-      <c r="S47" s="4"/>
-      <c r="T47" s="3"/>
-      <c r="U47" s="4"/>
+      <c r="R47" s="2">
+        <v>0</v>
+      </c>
+      <c r="S47" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="T47" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U47" s="4" t="s">
+        <v>488</v>
+      </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="B48" s="3"/>
-      <c r="C48" s="4"/>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="4"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="4"/>
-      <c r="K48" s="4"/>
-      <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
-      <c r="N48" s="2"/>
+        <v>489</v>
+      </c>
+      <c r="B48" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O48" s="3"/>
-      <c r="P48" s="2"/>
+      <c r="P48" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q48" s="3"/>
-      <c r="R48" s="2"/>
-      <c r="S48" s="4"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="4"/>
+      <c r="R48" s="2">
+        <v>0</v>
+      </c>
+      <c r="S48" s="4" t="s">
+        <v>497</v>
+      </c>
+      <c r="T48" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="4"/>
-      <c r="I49" s="2"/>
-      <c r="J49" s="4"/>
-      <c r="K49" s="4"/>
-      <c r="L49" s="2"/>
-      <c r="M49" s="2"/>
-      <c r="N49" s="2"/>
+        <v>499</v>
+      </c>
+      <c r="B49" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>501</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>504</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N49" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O49" s="3"/>
-      <c r="P49" s="2"/>
+      <c r="P49" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q49" s="3"/>
-      <c r="R49" s="2"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="4"/>
+      <c r="R49" s="2">
+        <v>0</v>
+      </c>
+      <c r="S49" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="T49" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U49" s="4" t="s">
+        <v>508</v>
+      </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="B50" s="3"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="4"/>
-      <c r="I50" s="2"/>
-      <c r="J50" s="4"/>
-      <c r="K50" s="4"/>
-      <c r="L50" s="2"/>
-      <c r="M50" s="2"/>
-      <c r="N50" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="B50" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H50" s="4" t="s">
+        <v>514</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N50" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O50" s="3"/>
-      <c r="P50" s="2"/>
+      <c r="P50" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q50" s="3"/>
-      <c r="R50" s="2"/>
-      <c r="S50" s="4"/>
-      <c r="T50" s="3"/>
-      <c r="U50" s="4"/>
+      <c r="R50" s="2">
+        <v>0</v>
+      </c>
+      <c r="S50" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="T50" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U50" s="4" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="2"/>
-      <c r="H51" s="4"/>
-      <c r="I51" s="2"/>
-      <c r="J51" s="4"/>
-      <c r="K51" s="4"/>
-      <c r="L51" s="2"/>
-      <c r="M51" s="2"/>
-      <c r="N51" s="2"/>
+        <v>519</v>
+      </c>
+      <c r="B51" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="E51" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H51" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="L51" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M51" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N51" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O51" s="3"/>
-      <c r="P51" s="2"/>
+      <c r="P51" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q51" s="3"/>
-      <c r="R51" s="2"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="3"/>
-      <c r="U51" s="4"/>
+      <c r="R51" s="2">
+        <v>0</v>
+      </c>
+      <c r="S51" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="T51" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U51" s="4" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B52" s="3"/>
-      <c r="C52" s="4"/>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="4"/>
-      <c r="I52" s="2"/>
-      <c r="J52" s="4"/>
-      <c r="K52" s="4"/>
-      <c r="L52" s="2"/>
-      <c r="M52" s="2"/>
-      <c r="N52" s="2"/>
+        <v>529</v>
+      </c>
+      <c r="B52" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O52" s="3"/>
-      <c r="P52" s="2"/>
+      <c r="P52" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q52" s="3"/>
-      <c r="R52" s="2"/>
-      <c r="S52" s="4"/>
-      <c r="T52" s="3"/>
-      <c r="U52" s="4"/>
+      <c r="R52" s="2">
+        <v>0</v>
+      </c>
+      <c r="S52" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="T52" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>538</v>
+      </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="4"/>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="4"/>
-      <c r="I53" s="2"/>
-      <c r="J53" s="4"/>
-      <c r="K53" s="4"/>
-      <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="B53" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="E53" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" s="4" t="s">
+        <v>544</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="L53" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O53" s="3"/>
-      <c r="P53" s="2"/>
+      <c r="P53" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q53" s="3"/>
-      <c r="R53" s="2"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="3"/>
-      <c r="U53" s="4"/>
+      <c r="R53" s="2">
+        <v>0</v>
+      </c>
+      <c r="S53" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="T53" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U53" s="4" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="B54" s="3"/>
-      <c r="C54" s="4"/>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="4"/>
-      <c r="I54" s="2"/>
-      <c r="J54" s="4"/>
-      <c r="K54" s="4"/>
-      <c r="L54" s="2"/>
-      <c r="M54" s="2"/>
-      <c r="N54" s="2"/>
+        <v>549</v>
+      </c>
+      <c r="B54" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>551</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>553</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>556</v>
+      </c>
+      <c r="L54" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N54" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O54" s="3"/>
-      <c r="P54" s="2"/>
+      <c r="P54" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q54" s="3"/>
-      <c r="R54" s="2"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="3"/>
-      <c r="U54" s="4"/>
+      <c r="R54" s="2">
+        <v>0</v>
+      </c>
+      <c r="S54" s="4" t="s">
+        <v>557</v>
+      </c>
+      <c r="T54" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>558</v>
+      </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="4"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="4"/>
-      <c r="K55" s="4"/>
-      <c r="L55" s="2"/>
-      <c r="M55" s="2"/>
-      <c r="N55" s="2"/>
+        <v>559</v>
+      </c>
+      <c r="B55" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>561</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>563</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H55" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>565</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>566</v>
+      </c>
+      <c r="L55" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M55" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O55" s="3"/>
-      <c r="P55" s="2"/>
+      <c r="P55" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q55" s="3"/>
-      <c r="R55" s="2"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="4"/>
+      <c r="R55" s="2">
+        <v>0</v>
+      </c>
+      <c r="S55" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="T55" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U55" s="4" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="B56" s="3"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="4"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="4"/>
-      <c r="K56" s="4"/>
-      <c r="L56" s="2"/>
-      <c r="M56" s="2"/>
-      <c r="N56" s="2"/>
+        <v>569</v>
+      </c>
+      <c r="B56" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="E56" s="4" t="s">
+        <v>572</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="L56" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M56" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N56" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O56" s="3"/>
-      <c r="P56" s="2"/>
+      <c r="P56" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q56" s="3"/>
-      <c r="R56" s="2"/>
-      <c r="S56" s="4"/>
-      <c r="T56" s="3"/>
-      <c r="U56" s="4"/>
+      <c r="R56" s="2">
+        <v>0</v>
+      </c>
+      <c r="S56" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="T56" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U56" s="4" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="B57" s="3"/>
-      <c r="C57" s="4"/>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="4"/>
-      <c r="I57" s="2"/>
-      <c r="J57" s="4"/>
-      <c r="K57" s="4"/>
-      <c r="L57" s="2"/>
-      <c r="M57" s="2"/>
-      <c r="N57" s="2"/>
+        <v>579</v>
+      </c>
+      <c r="B57" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H57" s="4" t="s">
+        <v>584</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="L57" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M57" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N57" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O57" s="3"/>
-      <c r="P57" s="2"/>
+      <c r="P57" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q57" s="3"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="3"/>
-      <c r="U57" s="4"/>
+      <c r="R57" s="2">
+        <v>0</v>
+      </c>
+      <c r="S57" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="T57" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U57" s="4" t="s">
+        <v>588</v>
+      </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="B58" s="3"/>
-      <c r="C58" s="4"/>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="4"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="4"/>
-      <c r="K58" s="4"/>
-      <c r="L58" s="2"/>
-      <c r="M58" s="2"/>
-      <c r="N58" s="2"/>
+        <v>589</v>
+      </c>
+      <c r="B58" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="L58" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N58" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O58" s="3"/>
-      <c r="P58" s="2"/>
+      <c r="P58" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q58" s="3"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="3"/>
-      <c r="U58" s="4"/>
+      <c r="R58" s="2">
+        <v>0</v>
+      </c>
+      <c r="S58" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="T58" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U58" s="4" t="s">
+        <v>598</v>
+      </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="B59" s="3"/>
-      <c r="C59" s="4"/>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="4"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="4"/>
-      <c r="K59" s="4"/>
-      <c r="L59" s="2"/>
-      <c r="M59" s="2"/>
-      <c r="N59" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="B59" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="E59" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="F59" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="J59" s="4" t="s">
+        <v>605</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="L59" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M59" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N59" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O59" s="3"/>
-      <c r="P59" s="2"/>
+      <c r="P59" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q59" s="3"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="4"/>
-      <c r="T59" s="3"/>
-      <c r="U59" s="4"/>
+      <c r="R59" s="2">
+        <v>0</v>
+      </c>
+      <c r="S59" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="T59" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U59" s="4" t="s">
+        <v>608</v>
+      </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="B60" s="3"/>
-      <c r="C60" s="4"/>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="4"/>
-      <c r="I60" s="2"/>
-      <c r="J60" s="4"/>
-      <c r="K60" s="4"/>
-      <c r="L60" s="2"/>
-      <c r="M60" s="2"/>
-      <c r="N60" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="B60" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H60" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J60" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="L60" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M60" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N60" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O60" s="3"/>
-      <c r="P60" s="2"/>
+      <c r="P60" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q60" s="3"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="3"/>
-      <c r="U60" s="4"/>
+      <c r="R60" s="2">
+        <v>0</v>
+      </c>
+      <c r="S60" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="T60" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U60" s="4" t="s">
+        <v>617</v>
+      </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="4"/>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="4"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="4"/>
-      <c r="K61" s="4"/>
-      <c r="L61" s="2"/>
-      <c r="M61" s="2"/>
-      <c r="N61" s="2"/>
+        <v>618</v>
+      </c>
+      <c r="B61" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>620</v>
+      </c>
+      <c r="E61" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>623</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J61" s="4" t="s">
+        <v>624</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="L61" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M61" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N61" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O61" s="3"/>
-      <c r="P61" s="2"/>
+      <c r="P61" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q61" s="3"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="3"/>
-      <c r="U61" s="4"/>
+      <c r="R61" s="2">
+        <v>0</v>
+      </c>
+      <c r="S61" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="T61" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U61" s="4" t="s">
+        <v>627</v>
+      </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B62" s="3"/>
-      <c r="C62" s="4"/>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="4"/>
-      <c r="I62" s="2"/>
-      <c r="J62" s="4"/>
-      <c r="K62" s="4"/>
-      <c r="L62" s="2"/>
-      <c r="M62" s="2"/>
-      <c r="N62" s="2"/>
+        <v>628</v>
+      </c>
+      <c r="B62" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>630</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>631</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H62" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>634</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M62" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N62" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O62" s="3"/>
-      <c r="P62" s="2"/>
+      <c r="P62" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q62" s="3"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="4"/>
-      <c r="T62" s="3"/>
-      <c r="U62" s="4"/>
+      <c r="R62" s="2">
+        <v>0</v>
+      </c>
+      <c r="S62" s="4" t="s">
+        <v>636</v>
+      </c>
+      <c r="T62" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U62" s="4" t="s">
+        <v>637</v>
+      </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="B63" s="3"/>
-      <c r="C63" s="4"/>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="4"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="4"/>
-      <c r="K63" s="4"/>
-      <c r="L63" s="2"/>
-      <c r="M63" s="2"/>
-      <c r="N63" s="2"/>
+        <v>638</v>
+      </c>
+      <c r="B63" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>640</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>641</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>644</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>645</v>
+      </c>
+      <c r="L63" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M63" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N63" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O63" s="3"/>
-      <c r="P63" s="2"/>
+      <c r="P63" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q63" s="3"/>
-      <c r="R63" s="2"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="3"/>
-      <c r="U63" s="4"/>
+      <c r="R63" s="2">
+        <v>0</v>
+      </c>
+      <c r="S63" s="4" t="s">
+        <v>646</v>
+      </c>
+      <c r="T63" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U63" s="4" t="s">
+        <v>647</v>
+      </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="B64" s="3"/>
-      <c r="C64" s="4"/>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="4"/>
-      <c r="I64" s="2"/>
-      <c r="J64" s="4"/>
-      <c r="K64" s="4"/>
-      <c r="L64" s="2"/>
-      <c r="M64" s="2"/>
-      <c r="N64" s="2"/>
+        <v>648</v>
+      </c>
+      <c r="B64" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H64" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="L64" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M64" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N64" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O64" s="3"/>
-      <c r="P64" s="2"/>
+      <c r="P64" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q64" s="3"/>
-      <c r="R64" s="2"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="3"/>
-      <c r="U64" s="4"/>
+      <c r="R64" s="2">
+        <v>0</v>
+      </c>
+      <c r="S64" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="T64" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U64" s="4" t="s">
+        <v>657</v>
+      </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="B65" s="3"/>
-      <c r="C65" s="4"/>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="4"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="4"/>
-      <c r="K65" s="4"/>
-      <c r="L65" s="2"/>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
+        <v>658</v>
+      </c>
+      <c r="B65" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H65" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="L65" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N65" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O65" s="3"/>
-      <c r="P65" s="2"/>
+      <c r="P65" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q65" s="3"/>
-      <c r="R65" s="2"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="3"/>
-      <c r="U65" s="4"/>
+      <c r="R65" s="2">
+        <v>0</v>
+      </c>
+      <c r="S65" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="T65" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U65" s="4" t="s">
+        <v>667</v>
+      </c>
     </row>
     <row r="66" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="B66" s="3"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="4"/>
-      <c r="I66" s="2"/>
-      <c r="J66" s="4"/>
-      <c r="K66" s="4"/>
-      <c r="L66" s="2"/>
-      <c r="M66" s="2"/>
-      <c r="N66" s="2"/>
+        <v>668</v>
+      </c>
+      <c r="B66" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="L66" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M66" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N66" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O66" s="3"/>
-      <c r="P66" s="2"/>
+      <c r="P66" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q66" s="3"/>
-      <c r="R66" s="2"/>
-      <c r="S66" s="4"/>
-      <c r="T66" s="3"/>
-      <c r="U66" s="4"/>
+      <c r="R66" s="2">
+        <v>0</v>
+      </c>
+      <c r="S66" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="T66" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U66" s="4" t="s">
+        <v>677</v>
+      </c>
     </row>
     <row r="67" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="B67" s="3"/>
-      <c r="C67" s="4"/>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="4"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="4"/>
-      <c r="K67" s="4"/>
-      <c r="L67" s="2"/>
-      <c r="M67" s="2"/>
-      <c r="N67" s="2"/>
+        <v>678</v>
+      </c>
+      <c r="B67" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="L67" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M67" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N67" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O67" s="3"/>
-      <c r="P67" s="2"/>
+      <c r="P67" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q67" s="3"/>
-      <c r="R67" s="2"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="3"/>
-      <c r="U67" s="4"/>
+      <c r="R67" s="2">
+        <v>0</v>
+      </c>
+      <c r="S67" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="T67" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U67" s="4" t="s">
+        <v>687</v>
+      </c>
     </row>
     <row r="68" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="B68" s="3"/>
-      <c r="C68" s="4"/>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="4"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="4"/>
-      <c r="K68" s="4"/>
-      <c r="L68" s="2"/>
-      <c r="M68" s="2"/>
-      <c r="N68" s="2"/>
+        <v>688</v>
+      </c>
+      <c r="B68" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E68" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="F68" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="L68" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M68" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N68" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O68" s="3"/>
-      <c r="P68" s="2"/>
+      <c r="P68" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q68" s="3"/>
-      <c r="R68" s="2"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="3"/>
-      <c r="U68" s="4"/>
+      <c r="R68" s="2">
+        <v>0</v>
+      </c>
+      <c r="S68" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="T68" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U68" s="4" t="s">
+        <v>697</v>
+      </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="B69" s="3"/>
-      <c r="C69" s="4"/>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="4"/>
-      <c r="I69" s="2"/>
-      <c r="J69" s="4"/>
-      <c r="K69" s="4"/>
-      <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
-      <c r="N69" s="2"/>
+        <v>698</v>
+      </c>
+      <c r="B69" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="E69" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="F69" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="L69" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M69" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N69" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O69" s="3"/>
-      <c r="P69" s="2"/>
+      <c r="P69" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q69" s="3"/>
-      <c r="R69" s="2"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="3"/>
-      <c r="U69" s="4"/>
+      <c r="R69" s="2">
+        <v>0</v>
+      </c>
+      <c r="S69" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="T69" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U69" s="4" t="s">
+        <v>707</v>
+      </c>
     </row>
     <row r="70" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="B70" s="3"/>
-      <c r="C70" s="4"/>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="4"/>
-      <c r="I70" s="2"/>
-      <c r="J70" s="4"/>
-      <c r="K70" s="4"/>
-      <c r="L70" s="2"/>
-      <c r="M70" s="2"/>
-      <c r="N70" s="2"/>
+        <v>708</v>
+      </c>
+      <c r="B70" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H70" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>715</v>
+      </c>
+      <c r="L70" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M70" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N70" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O70" s="3"/>
-      <c r="P70" s="2"/>
+      <c r="P70" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q70" s="3"/>
-      <c r="R70" s="2"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="3"/>
-      <c r="U70" s="4"/>
+      <c r="R70" s="2">
+        <v>0</v>
+      </c>
+      <c r="S70" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="T70" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U70" s="4" t="s">
+        <v>717</v>
+      </c>
     </row>
     <row r="71" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="B71" s="3"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="4"/>
-      <c r="I71" s="2"/>
-      <c r="J71" s="4"/>
-      <c r="K71" s="4"/>
-      <c r="L71" s="2"/>
-      <c r="M71" s="2"/>
-      <c r="N71" s="2"/>
+        <v>718</v>
+      </c>
+      <c r="B71" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>719</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>720</v>
+      </c>
+      <c r="E71" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H71" s="4" t="s">
+        <v>723</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>724</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>725</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M71" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N71" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O71" s="3"/>
-      <c r="P71" s="2"/>
+      <c r="P71" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q71" s="3"/>
-      <c r="R71" s="2"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="3"/>
-      <c r="U71" s="4"/>
+      <c r="R71" s="2">
+        <v>0</v>
+      </c>
+      <c r="S71" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="T71" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U71" s="4" t="s">
+        <v>727</v>
+      </c>
     </row>
     <row r="72" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B72" s="3"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="2"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="2"/>
-      <c r="M72" s="2"/>
-      <c r="N72" s="2"/>
+        <v>728</v>
+      </c>
+      <c r="B72" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>729</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="E72" s="4" t="s">
+        <v>731</v>
+      </c>
+      <c r="F72" s="4" t="s">
+        <v>732</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>735</v>
+      </c>
+      <c r="L72" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M72" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N72" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O72" s="3"/>
-      <c r="P72" s="2"/>
+      <c r="P72" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q72" s="3"/>
-      <c r="R72" s="2"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="3"/>
-      <c r="U72" s="4"/>
+      <c r="R72" s="2">
+        <v>0</v>
+      </c>
+      <c r="S72" s="4" t="s">
+        <v>736</v>
+      </c>
+      <c r="T72" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U72" s="4" t="s">
+        <v>737</v>
+      </c>
     </row>
     <row r="73" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="B73" s="3"/>
-      <c r="C73" s="4"/>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="4"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="4"/>
-      <c r="K73" s="4"/>
-      <c r="L73" s="2"/>
-      <c r="M73" s="2"/>
-      <c r="N73" s="2"/>
+        <v>738</v>
+      </c>
+      <c r="B73" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>739</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>740</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H73" s="4" t="s">
+        <v>743</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>744</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="L73" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M73" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N73" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O73" s="3"/>
-      <c r="P73" s="2"/>
+      <c r="P73" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q73" s="3"/>
-      <c r="R73" s="2"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="3"/>
-      <c r="U73" s="4"/>
+      <c r="R73" s="2">
+        <v>0</v>
+      </c>
+      <c r="S73" s="4" t="s">
+        <v>746</v>
+      </c>
+      <c r="T73" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U73" s="4" t="s">
+        <v>747</v>
+      </c>
     </row>
     <row r="74" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="B74" s="3"/>
-      <c r="C74" s="4"/>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="4"/>
-      <c r="I74" s="2"/>
-      <c r="J74" s="4"/>
-      <c r="K74" s="4"/>
-      <c r="L74" s="2"/>
-      <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
+        <v>748</v>
+      </c>
+      <c r="B74" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>749</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>750</v>
+      </c>
+      <c r="E74" s="4" t="s">
+        <v>751</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>752</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H74" s="4" t="s">
+        <v>753</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>754</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>755</v>
+      </c>
+      <c r="L74" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M74" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N74" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O74" s="3"/>
-      <c r="P74" s="2"/>
+      <c r="P74" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q74" s="3"/>
-      <c r="R74" s="2"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="3"/>
-      <c r="U74" s="4"/>
+      <c r="R74" s="2">
+        <v>0</v>
+      </c>
+      <c r="S74" s="4" t="s">
+        <v>756</v>
+      </c>
+      <c r="T74" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U74" s="4" t="s">
+        <v>757</v>
+      </c>
     </row>
     <row r="75" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="B75" s="3"/>
-      <c r="C75" s="4"/>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="4"/>
-      <c r="I75" s="2"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="4"/>
-      <c r="L75" s="2"/>
-      <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
+        <v>758</v>
+      </c>
+      <c r="B75" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>759</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>760</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>761</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>762</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>763</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M75" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N75" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O75" s="3"/>
-      <c r="P75" s="2"/>
+      <c r="P75" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q75" s="3"/>
-      <c r="R75" s="2"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="3"/>
-      <c r="U75" s="4"/>
+      <c r="R75" s="2">
+        <v>0</v>
+      </c>
+      <c r="S75" s="4" t="s">
+        <v>766</v>
+      </c>
+      <c r="T75" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U75" s="4" t="s">
+        <v>767</v>
+      </c>
     </row>
     <row r="76" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="B76" s="3"/>
-      <c r="C76" s="4"/>
-      <c r="D76" s="4"/>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="4"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="4"/>
-      <c r="L76" s="2"/>
-      <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
+        <v>768</v>
+      </c>
+      <c r="B76" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>769</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>770</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>771</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>772</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>773</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>774</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="L76" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M76" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N76" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O76" s="3"/>
-      <c r="P76" s="2"/>
+      <c r="P76" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q76" s="3"/>
-      <c r="R76" s="2"/>
-      <c r="S76" s="4"/>
-      <c r="T76" s="3"/>
-      <c r="U76" s="4"/>
+      <c r="R76" s="2">
+        <v>0</v>
+      </c>
+      <c r="S76" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="T76" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U76" s="4" t="s">
+        <v>777</v>
+      </c>
     </row>
     <row r="77" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="B77" s="3"/>
-      <c r="C77" s="4"/>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="4"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="4"/>
-      <c r="K77" s="4"/>
-      <c r="L77" s="2"/>
-      <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
+        <v>778</v>
+      </c>
+      <c r="B77" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="E77" s="4" t="s">
+        <v>781</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="L77" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M77" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N77" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O77" s="3"/>
-      <c r="P77" s="2"/>
+      <c r="P77" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q77" s="3"/>
-      <c r="R77" s="2"/>
-      <c r="S77" s="4"/>
-      <c r="T77" s="3"/>
-      <c r="U77" s="4"/>
+      <c r="R77" s="2">
+        <v>0</v>
+      </c>
+      <c r="S77" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="T77" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U77" s="4" t="s">
+        <v>787</v>
+      </c>
     </row>
     <row r="78" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="B78" s="3"/>
-      <c r="C78" s="4"/>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="4"/>
-      <c r="I78" s="2"/>
-      <c r="J78" s="4"/>
-      <c r="K78" s="4"/>
-      <c r="L78" s="2"/>
-      <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
+        <v>788</v>
+      </c>
+      <c r="B78" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="L78" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M78" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N78" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O78" s="3"/>
-      <c r="P78" s="2"/>
+      <c r="P78" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q78" s="3"/>
-      <c r="R78" s="2"/>
-      <c r="S78" s="4"/>
-      <c r="T78" s="3"/>
-      <c r="U78" s="4"/>
+      <c r="R78" s="2">
+        <v>0</v>
+      </c>
+      <c r="S78" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="T78" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U78" s="4" t="s">
+        <v>797</v>
+      </c>
     </row>
     <row r="79" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="B79" s="3"/>
-      <c r="C79" s="4"/>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="4"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="4"/>
-      <c r="K79" s="4"/>
-      <c r="L79" s="2"/>
-      <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
+        <v>798</v>
+      </c>
+      <c r="B79" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>802</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>803</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>804</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>805</v>
+      </c>
+      <c r="L79" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M79" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N79" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O79" s="3"/>
-      <c r="P79" s="2"/>
+      <c r="P79" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q79" s="3"/>
-      <c r="R79" s="2"/>
-      <c r="S79" s="4"/>
-      <c r="T79" s="3"/>
-      <c r="U79" s="4"/>
+      <c r="R79" s="2">
+        <v>0</v>
+      </c>
+      <c r="S79" s="4" t="s">
+        <v>806</v>
+      </c>
+      <c r="T79" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U79" s="4" t="s">
+        <v>807</v>
+      </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="B80" s="3"/>
-      <c r="C80" s="4"/>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="4"/>
-      <c r="I80" s="2"/>
-      <c r="J80" s="4"/>
-      <c r="K80" s="4"/>
-      <c r="L80" s="2"/>
-      <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
+        <v>808</v>
+      </c>
+      <c r="B80" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>809</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>810</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>812</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>815</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M80" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N80" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O80" s="3"/>
-      <c r="P80" s="2"/>
+      <c r="P80" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q80" s="3"/>
-      <c r="R80" s="2"/>
-      <c r="S80" s="4"/>
-      <c r="T80" s="3"/>
-      <c r="U80" s="4"/>
+      <c r="R80" s="2">
+        <v>0</v>
+      </c>
+      <c r="S80" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="T80" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U80" s="4" t="s">
+        <v>817</v>
+      </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="4"/>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
-      <c r="G81" s="2"/>
-      <c r="H81" s="4"/>
-      <c r="I81" s="2"/>
-      <c r="J81" s="4"/>
-      <c r="K81" s="4"/>
-      <c r="L81" s="2"/>
-      <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
+        <v>818</v>
+      </c>
+      <c r="B81" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>820</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>824</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="L81" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M81" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N81" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O81" s="3"/>
-      <c r="P81" s="2"/>
+      <c r="P81" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q81" s="3"/>
-      <c r="R81" s="2"/>
-      <c r="S81" s="4"/>
-      <c r="T81" s="3"/>
-      <c r="U81" s="4"/>
+      <c r="R81" s="2">
+        <v>0</v>
+      </c>
+      <c r="S81" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="T81" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U81" s="4" t="s">
+        <v>828</v>
+      </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="B82" s="3"/>
-      <c r="C82" s="4"/>
-      <c r="D82" s="4"/>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="4"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="4"/>
-      <c r="K82" s="4"/>
-      <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
+        <v>829</v>
+      </c>
+      <c r="B82" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="E82" s="4" t="s">
+        <v>832</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>836</v>
+      </c>
+      <c r="L82" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M82" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N82" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O82" s="3"/>
-      <c r="P82" s="2"/>
+      <c r="P82" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q82" s="3"/>
-      <c r="R82" s="2"/>
-      <c r="S82" s="4"/>
-      <c r="T82" s="3"/>
-      <c r="U82" s="4"/>
+      <c r="R82" s="2">
+        <v>0</v>
+      </c>
+      <c r="S82" s="4" t="s">
+        <v>837</v>
+      </c>
+      <c r="T82" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U82" s="4" t="s">
+        <v>838</v>
+      </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="4"/>
-      <c r="D83" s="4"/>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="4"/>
-      <c r="I83" s="2"/>
-      <c r="J83" s="4"/>
-      <c r="K83" s="4"/>
-      <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
+        <v>839</v>
+      </c>
+      <c r="B83" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="E83" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="I83" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J83" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="L83" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M83" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N83" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O83" s="3"/>
-      <c r="P83" s="2"/>
+      <c r="P83" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q83" s="3"/>
-      <c r="R83" s="2"/>
-      <c r="S83" s="4"/>
-      <c r="T83" s="3"/>
-      <c r="U83" s="4"/>
+      <c r="R83" s="2">
+        <v>0</v>
+      </c>
+      <c r="S83" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="T83" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U83" s="4" t="s">
+        <v>848</v>
+      </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="B84" s="3"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="4"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="4"/>
-      <c r="K84" s="4"/>
-      <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
+        <v>849</v>
+      </c>
+      <c r="B84" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J84" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="L84" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M84" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O84" s="3"/>
-      <c r="P84" s="2"/>
+      <c r="P84" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q84" s="3"/>
-      <c r="R84" s="2"/>
-      <c r="S84" s="4"/>
-      <c r="T84" s="3"/>
-      <c r="U84" s="4"/>
+      <c r="R84" s="2">
+        <v>0</v>
+      </c>
+      <c r="S84" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="T84" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U84" s="4" t="s">
+        <v>857</v>
+      </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="B85" s="3"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="4"/>
-      <c r="I85" s="2"/>
-      <c r="J85" s="4"/>
-      <c r="K85" s="4"/>
-      <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
+        <v>858</v>
+      </c>
+      <c r="B85" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J85" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="L85" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M85" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N85" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O85" s="3"/>
-      <c r="P85" s="2"/>
+      <c r="P85" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q85" s="3"/>
-      <c r="R85" s="2"/>
-      <c r="S85" s="4"/>
-      <c r="T85" s="3"/>
-      <c r="U85" s="4"/>
+      <c r="R85" s="2">
+        <v>0</v>
+      </c>
+      <c r="S85" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="T85" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U85" s="4" t="s">
+        <v>867</v>
+      </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="B86" s="3"/>
-      <c r="C86" s="4"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="4"/>
-      <c r="I86" s="2"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="4"/>
-      <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
-      <c r="N86" s="2"/>
+        <v>868</v>
+      </c>
+      <c r="B86" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H86" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J86" s="4" t="s">
+        <v>874</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="L86" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M86" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N86" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O86" s="3"/>
-      <c r="P86" s="2"/>
+      <c r="P86" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q86" s="3"/>
-      <c r="R86" s="2"/>
-      <c r="S86" s="4"/>
-      <c r="T86" s="3"/>
-      <c r="U86" s="4"/>
+      <c r="R86" s="2">
+        <v>0</v>
+      </c>
+      <c r="S86" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="T86" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U86" s="4" t="s">
+        <v>877</v>
+      </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="B87" s="3"/>
-      <c r="C87" s="4"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="4"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="4"/>
-      <c r="K87" s="4"/>
-      <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
+        <v>878</v>
+      </c>
+      <c r="B87" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J87" s="4" t="s">
+        <v>884</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M87" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N87" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O87" s="3"/>
-      <c r="P87" s="2"/>
+      <c r="P87" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q87" s="3"/>
-      <c r="R87" s="2"/>
-      <c r="S87" s="4"/>
-      <c r="T87" s="3"/>
-      <c r="U87" s="4"/>
+      <c r="R87" s="2">
+        <v>0</v>
+      </c>
+      <c r="S87" s="4" t="s">
+        <v>886</v>
+      </c>
+      <c r="T87" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U87" s="4" t="s">
+        <v>887</v>
+      </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="B88" s="3"/>
-      <c r="C88" s="4"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="4"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="4"/>
-      <c r="K88" s="4"/>
-      <c r="L88" s="2"/>
-      <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
+        <v>888</v>
+      </c>
+      <c r="B88" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>890</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J88" s="4" t="s">
+        <v>894</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M88" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N88" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O88" s="3"/>
-      <c r="P88" s="2"/>
+      <c r="P88" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q88" s="3"/>
-      <c r="R88" s="2"/>
-      <c r="S88" s="4"/>
-      <c r="T88" s="3"/>
-      <c r="U88" s="4"/>
+      <c r="R88" s="2">
+        <v>0</v>
+      </c>
+      <c r="S88" s="4" t="s">
+        <v>896</v>
+      </c>
+      <c r="T88" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U88" s="4" t="s">
+        <v>897</v>
+      </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="B89" s="3"/>
-      <c r="C89" s="4"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="4"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="4"/>
-      <c r="K89" s="4"/>
-      <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
+        <v>898</v>
+      </c>
+      <c r="B89" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>900</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J89" s="4" t="s">
+        <v>904</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="L89" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M89" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O89" s="3"/>
-      <c r="P89" s="2"/>
+      <c r="P89" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q89" s="3"/>
-      <c r="R89" s="2"/>
-      <c r="S89" s="4"/>
-      <c r="T89" s="3"/>
-      <c r="U89" s="4"/>
+      <c r="R89" s="2">
+        <v>0</v>
+      </c>
+      <c r="S89" s="4" t="s">
+        <v>906</v>
+      </c>
+      <c r="T89" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U89" s="4" t="s">
+        <v>907</v>
+      </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="B90" s="3"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="4"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="4"/>
-      <c r="K90" s="4"/>
-      <c r="L90" s="2"/>
-      <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
+        <v>908</v>
+      </c>
+      <c r="B90" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>912</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J90" s="4" t="s">
+        <v>914</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="L90" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M90" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N90" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O90" s="3"/>
-      <c r="P90" s="2"/>
+      <c r="P90" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q90" s="3"/>
-      <c r="R90" s="2"/>
-      <c r="S90" s="4"/>
-      <c r="T90" s="3"/>
-      <c r="U90" s="4"/>
+      <c r="R90" s="2">
+        <v>0</v>
+      </c>
+      <c r="S90" s="4" t="s">
+        <v>916</v>
+      </c>
+      <c r="T90" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U90" s="4" t="s">
+        <v>917</v>
+      </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="B91" s="3"/>
-      <c r="C91" s="4"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="4"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="4"/>
-      <c r="K91" s="4"/>
-      <c r="L91" s="2"/>
-      <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
+        <v>918</v>
+      </c>
+      <c r="B91" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>919</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>921</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>923</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J91" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>925</v>
+      </c>
+      <c r="L91" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M91" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N91" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O91" s="3"/>
-      <c r="P91" s="2"/>
+      <c r="P91" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q91" s="3"/>
-      <c r="R91" s="2"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="3"/>
-      <c r="U91" s="4"/>
+      <c r="R91" s="2">
+        <v>0</v>
+      </c>
+      <c r="S91" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="T91" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U91" s="4" t="s">
+        <v>927</v>
+      </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="4"/>
-      <c r="D92" s="4"/>
-      <c r="E92" s="4"/>
-      <c r="F92" s="4"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="4"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="4"/>
-      <c r="K92" s="4"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
+        <v>928</v>
+      </c>
+      <c r="B92" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>932</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J92" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="L92" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M92" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N92" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O92" s="3"/>
-      <c r="P92" s="2"/>
+      <c r="P92" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q92" s="3"/>
-      <c r="R92" s="2"/>
-      <c r="S92" s="4"/>
-      <c r="T92" s="3"/>
-      <c r="U92" s="4"/>
+      <c r="R92" s="2">
+        <v>0</v>
+      </c>
+      <c r="S92" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="T92" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U92" s="4" t="s">
+        <v>937</v>
+      </c>
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="B93" s="3"/>
-      <c r="C93" s="4"/>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="4"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="4"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="4"/>
-      <c r="K93" s="4"/>
-      <c r="L93" s="2"/>
-      <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
+        <v>938</v>
+      </c>
+      <c r="B93" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>943</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J93" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>940</v>
+      </c>
+      <c r="L93" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M93" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N93" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O93" s="3"/>
-      <c r="P93" s="2"/>
+      <c r="P93" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q93" s="3"/>
-      <c r="R93" s="2"/>
-      <c r="S93" s="4"/>
-      <c r="T93" s="3"/>
-      <c r="U93" s="4"/>
+      <c r="R93" s="2">
+        <v>0</v>
+      </c>
+      <c r="S93" s="4" t="s">
+        <v>945</v>
+      </c>
+      <c r="T93" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U93" s="4" t="s">
+        <v>946</v>
+      </c>
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="B94" s="3"/>
-      <c r="C94" s="4"/>
-      <c r="D94" s="4"/>
-      <c r="E94" s="4"/>
-      <c r="F94" s="4"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="4"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="4"/>
-      <c r="K94" s="4"/>
-      <c r="L94" s="2"/>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
+        <v>947</v>
+      </c>
+      <c r="B94" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>949</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>951</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>953</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="L94" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M94" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O94" s="3"/>
-      <c r="P94" s="2"/>
+      <c r="P94" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q94" s="3"/>
-      <c r="R94" s="2"/>
-      <c r="S94" s="4"/>
-      <c r="T94" s="3"/>
-      <c r="U94" s="4"/>
+      <c r="R94" s="2">
+        <v>0</v>
+      </c>
+      <c r="S94" s="4" t="s">
+        <v>955</v>
+      </c>
+      <c r="T94" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U94" s="4" t="s">
+        <v>956</v>
+      </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="B95" s="3"/>
-      <c r="C95" s="4"/>
-      <c r="D95" s="4"/>
-      <c r="E95" s="4"/>
-      <c r="F95" s="4"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="4"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="4"/>
-      <c r="K95" s="4"/>
-      <c r="L95" s="2"/>
-      <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
+        <v>957</v>
+      </c>
+      <c r="B95" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>961</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J95" s="4" t="s">
+        <v>963</v>
+      </c>
+      <c r="K95" s="4" t="s">
+        <v>959</v>
+      </c>
+      <c r="L95" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M95" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N95" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O95" s="3"/>
-      <c r="P95" s="2"/>
+      <c r="P95" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q95" s="3"/>
-      <c r="R95" s="2"/>
-      <c r="S95" s="4"/>
-      <c r="T95" s="3"/>
-      <c r="U95" s="4"/>
+      <c r="R95" s="2">
+        <v>0</v>
+      </c>
+      <c r="S95" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="T95" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U95" s="4" t="s">
+        <v>965</v>
+      </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="B96" s="3"/>
-      <c r="C96" s="4"/>
-      <c r="D96" s="4"/>
-      <c r="E96" s="4"/>
-      <c r="F96" s="4"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="4"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="4"/>
-      <c r="K96" s="4"/>
-      <c r="L96" s="2"/>
-      <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
+        <v>966</v>
+      </c>
+      <c r="B96" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>967</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>968</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>969</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>970</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>971</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J96" s="4" t="s">
+        <v>972</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="L96" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M96" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N96" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O96" s="3"/>
-      <c r="P96" s="2"/>
+      <c r="P96" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q96" s="3"/>
-      <c r="R96" s="2"/>
-      <c r="S96" s="4"/>
-      <c r="T96" s="3"/>
-      <c r="U96" s="4"/>
+      <c r="R96" s="2">
+        <v>0</v>
+      </c>
+      <c r="S96" s="4" t="s">
+        <v>974</v>
+      </c>
+      <c r="T96" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U96" s="4" t="s">
+        <v>975</v>
+      </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="B97" s="3"/>
-      <c r="C97" s="4"/>
-      <c r="D97" s="4"/>
-      <c r="E97" s="4"/>
-      <c r="F97" s="4"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="4"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="4"/>
-      <c r="K97" s="4"/>
-      <c r="L97" s="2"/>
-      <c r="M97" s="2"/>
-      <c r="N97" s="2"/>
+        <v>976</v>
+      </c>
+      <c r="B97" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>977</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>978</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>979</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H97" s="4" t="s">
+        <v>981</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>982</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>983</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>984</v>
+      </c>
+      <c r="L97" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M97" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N97" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O97" s="3"/>
-      <c r="P97" s="2"/>
+      <c r="P97" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q97" s="3"/>
-      <c r="R97" s="2"/>
-      <c r="S97" s="4"/>
-      <c r="T97" s="3"/>
-      <c r="U97" s="4"/>
+      <c r="R97" s="2">
+        <v>0</v>
+      </c>
+      <c r="S97" s="4" t="s">
+        <v>985</v>
+      </c>
+      <c r="T97" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U97" s="4" t="s">
+        <v>986</v>
+      </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="B98" s="3"/>
-      <c r="C98" s="4"/>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="4"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="4"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="4"/>
-      <c r="K98" s="4"/>
-      <c r="L98" s="2"/>
-      <c r="M98" s="2"/>
-      <c r="N98" s="2"/>
+        <v>987</v>
+      </c>
+      <c r="B98" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>988</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>989</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>990</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H98" s="4" t="s">
+        <v>992</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J98" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>994</v>
+      </c>
+      <c r="L98" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M98" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N98" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O98" s="3"/>
-      <c r="P98" s="2"/>
+      <c r="P98" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q98" s="3"/>
-      <c r="R98" s="2"/>
-      <c r="S98" s="4"/>
-      <c r="T98" s="3"/>
-      <c r="U98" s="4"/>
+      <c r="R98" s="2">
+        <v>0</v>
+      </c>
+      <c r="S98" s="4" t="s">
+        <v>995</v>
+      </c>
+      <c r="T98" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U98" s="4" t="s">
+        <v>996</v>
+      </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="B99" s="3"/>
-      <c r="C99" s="4"/>
-      <c r="D99" s="4"/>
-      <c r="E99" s="4"/>
-      <c r="F99" s="4"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="4"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="4"/>
-      <c r="K99" s="4"/>
-      <c r="L99" s="2"/>
-      <c r="M99" s="2"/>
-      <c r="N99" s="2"/>
+        <v>997</v>
+      </c>
+      <c r="B99" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>998</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>999</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>1001</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="J99" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="L99" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M99" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N99" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O99" s="3"/>
-      <c r="P99" s="2"/>
+      <c r="P99" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q99" s="3"/>
-      <c r="R99" s="2"/>
-      <c r="S99" s="4"/>
-      <c r="T99" s="3"/>
-      <c r="U99" s="4"/>
+      <c r="R99" s="2">
+        <v>0</v>
+      </c>
+      <c r="S99" s="4" t="s">
+        <v>1003</v>
+      </c>
+      <c r="T99" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U99" s="4" t="s">
+        <v>1004</v>
+      </c>
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="B100" s="3"/>
-      <c r="C100" s="4"/>
-      <c r="D100" s="4"/>
-      <c r="E100" s="4"/>
-      <c r="F100" s="4"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="4"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="4"/>
-      <c r="K100" s="4"/>
-      <c r="L100" s="2"/>
-      <c r="M100" s="2"/>
-      <c r="N100" s="2"/>
+        <v>1005</v>
+      </c>
+      <c r="B100" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>1007</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>1011</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="L100" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M100" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N100" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O100" s="3"/>
-      <c r="P100" s="2"/>
+      <c r="P100" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q100" s="3"/>
-      <c r="R100" s="2"/>
-      <c r="S100" s="4"/>
-      <c r="T100" s="3"/>
-      <c r="U100" s="4"/>
+      <c r="R100" s="2">
+        <v>0</v>
+      </c>
+      <c r="S100" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="T100" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U100" s="4" t="s">
+        <v>1014</v>
+      </c>
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="B101" s="3"/>
-      <c r="C101" s="4"/>
-      <c r="D101" s="4"/>
-      <c r="E101" s="4"/>
-      <c r="F101" s="4"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="4"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="4"/>
-      <c r="K101" s="4"/>
-      <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
-      <c r="N101" s="2"/>
+        <v>1015</v>
+      </c>
+      <c r="B101" s="3">
+        <v>46314</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J101" s="4" t="s">
+        <v>1021</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>1022</v>
+      </c>
+      <c r="L101" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="M101" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N101" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="O101" s="3"/>
-      <c r="P101" s="2"/>
+      <c r="P101" s="2" t="s">
+        <v>34</v>
+      </c>
       <c r="Q101" s="3"/>
-      <c r="R101" s="2"/>
-      <c r="S101" s="4"/>
-      <c r="T101" s="3"/>
-      <c r="U101" s="4"/>
+      <c r="R101" s="2">
+        <v>0</v>
+      </c>
+      <c r="S101" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="T101" s="3">
+        <v>46316</v>
+      </c>
+      <c r="U101" s="4" t="s">
+        <v>1024</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:U101"/>
@@ -4831,28 +9862,28 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>308</v>
+        <v>1025</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>309</v>
+        <v>1026</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>310</v>
+        <v>1027</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>1028</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>312</v>
+        <v>1029</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>313</v>
+        <v>1030</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>314</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -4929,8 +9960,12 @@
       <c r="A7" s="3">
         <v>46314</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
+      <c r="B7" s="5">
+        <v>80</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0</v>
+      </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -5129,22 +10164,22 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>315</v>
+        <v>1032</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>316</v>
+        <v>1033</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>317</v>
+        <v>1034</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>318</v>
+        <v>1035</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>319</v>
+        <v>1036</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>320</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="2" ht="65" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5152,10 +10187,10 @@
         <v>34</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>321</v>
+        <v>1038</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>322</v>
+        <v>1039</v>
       </c>
       <c r="D2" s="5">
         <v>0</v>
@@ -5169,13 +10204,13 @@
     </row>
     <row r="3" ht="65" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>323</v>
+        <v>1040</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>324</v>
+        <v>1041</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>325</v>
+        <v>1042</v>
       </c>
       <c r="D3" s="5">
         <v>0</v>
@@ -5189,13 +10224,13 @@
     </row>
     <row r="4" ht="65" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>326</v>
+        <v>1043</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>327</v>
+        <v>1044</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>328</v>
+        <v>1045</v>
       </c>
       <c r="D4" s="5">
         <v>0</v>
@@ -5209,13 +10244,13 @@
     </row>
     <row r="5" ht="65" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>329</v>
+        <v>1046</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>330</v>
+        <v>1047</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>331</v>
+        <v>1048</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -5254,42 +10289,42 @@
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>1049</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>309</v>
+        <v>1026</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>310</v>
+        <v>1027</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>1028</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>312</v>
+        <v>1029</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>313</v>
+        <v>1030</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>314</v>
+        <v>1031</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>320</v>
+        <v>1037</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>333</v>
+        <v>1050</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>334</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>335</v>
+        <v>1052</v>
       </c>
       <c r="B2" s="5">
         <f>SUM('Daily log'!B2:B6)</f>
@@ -5320,7 +10355,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>336</v>
+        <v>1053</v>
       </c>
       <c r="B3" s="5">
         <f>SUM('Daily log'!B7:B11)</f>
@@ -5351,7 +10386,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>337</v>
+        <v>1054</v>
       </c>
       <c r="B4" s="5">
         <f>SUM('Daily log'!B12:B16)</f>
@@ -5382,7 +10417,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>338</v>
+        <v>1055</v>
       </c>
       <c r="B5" s="5">
         <f>SUM('Daily log'!B17:B21)</f>
